--- a/dataset/数据.xlsx
+++ b/dataset/数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSBR\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1DC4BF-BCE4-407B-8C05-06F77E46D14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B3AB15-FA20-4C5D-9AA2-82165BF491EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2270" yWindow="1060" windowWidth="11290" windowHeight="9020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
     <t>核心官能团 SMILES</t>
   </si>
   <si>
-    <t>官能化程度（基于 SSBR 接枝百分比）</t>
-  </si>
-  <si>
     <t>核磁谱图</t>
   </si>
   <si>
@@ -224,6 +221,10 @@
   </si>
   <si>
     <t>-Si(OC2H5)3</t>
+  </si>
+  <si>
+    <t>官能化程度 (wt%)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -663,111 +664,111 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="H1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="18.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="4">
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P2">
         <v>1.5</v>
       </c>
       <c r="Q2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R2">
         <v>9</v>
@@ -779,69 +780,69 @@
         <v>452</v>
       </c>
       <c r="U2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V2">
         <v>-9</v>
       </c>
       <c r="W2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="18.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="H3" s="5">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="M3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="O3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P3">
         <v>4.2</v>
       </c>
       <c r="Q3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S3">
         <v>14.2</v>
@@ -850,66 +851,66 @@
         <v>200</v>
       </c>
       <c r="U3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V3">
         <v>-0.9</v>
       </c>
       <c r="W3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18.75" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="H4" s="5">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="M4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="O4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P4">
         <v>6.3</v>
       </c>
       <c r="Q4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R4">
         <v>23.3</v>
@@ -921,69 +922,69 @@
         <v>340</v>
       </c>
       <c r="U4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V4">
         <v>-2.1</v>
       </c>
       <c r="W4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="D5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="H5" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="M5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="O5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P5">
         <v>11</v>
       </c>
       <c r="Q5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S5">
         <v>11.9</v>
@@ -992,13 +993,13 @@
         <v>105</v>
       </c>
       <c r="U5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V5">
         <v>-1.1000000000000001</v>
       </c>
       <c r="W5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/数据.xlsx
+++ b/dataset/数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSBR\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B3AB15-FA20-4C5D-9AA2-82165BF491EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A719DC3B-0F4E-4FFD-B5CE-430C7C3C6C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2270" yWindow="1060" windowWidth="11290" windowHeight="9020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="83">
   <si>
     <t>样本ID</t>
   </si>
@@ -41,9 +41,6 @@
   </si>
   <si>
     <t>微相分离图片表征</t>
-  </si>
-  <si>
-    <t>应力 - 应变曲线</t>
   </si>
   <si>
     <t>DSC 谱图</t>
@@ -224,6 +221,65 @@
   </si>
   <si>
     <t>官能化程度 (wt%)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心力学图谱</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSBR-005</t>
+  </si>
+  <si>
+    <t>绿色轮胎/硅胶复合材料</t>
+  </si>
+  <si>
+    <t>0 wt%</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 NMR谱图</t>
+  </si>
+  <si>
+    <t>文献 Fig.8 TEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.6 Payne效应曲线及Fig.9 DMA曲线</t>
+  </si>
+  <si>
+    <t>文献 Fig.11 DSC曲线</t>
+  </si>
+  <si>
+    <t>10.1039_c4ra09492a_Qu_2014</t>
+  </si>
+  <si>
+    <t>SSBR-006</t>
+  </si>
+  <si>
+    <t>3-巯基丙酸（MPA）</t>
+  </si>
+  <si>
+    <t>O=C(O)CCS</t>
+  </si>
+  <si>
+    <t>SSBR-007</t>
+  </si>
+  <si>
+    <t>SSBR-008</t>
+  </si>
+  <si>
+    <t>Qu L, et al. Contribution of silica–rubber interactions on the viscoelastic behaviors of modified solution polymerized styrene butadiene rubbers (M-S-SBRs) f illed with silica. RSC Adv, 2014, 4(108): 64354-64363.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.40 wt%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.20 wt%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.60 wt%</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -627,7 +683,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -641,7 +697,7 @@
     <col min="10" max="10" width="52" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="52.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="41.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="194.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="230.54296875" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="29" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="29" customWidth="1"/>
     <col min="16" max="23" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -664,13 +720,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -679,96 +735,96 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="18.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" s="4">
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P2">
         <v>1.5</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R2">
         <v>9</v>
@@ -780,69 +836,69 @@
         <v>452</v>
       </c>
       <c r="U2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V2">
         <v>-9</v>
       </c>
       <c r="W2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="18.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="H3" s="5">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="M3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="O3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P3">
         <v>4.2</v>
       </c>
       <c r="Q3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S3">
         <v>14.2</v>
@@ -851,66 +907,66 @@
         <v>200</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V3">
         <v>-0.9</v>
       </c>
       <c r="W3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="18.75" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="H4" s="5">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="M4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="O4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P4">
         <v>6.3</v>
       </c>
       <c r="Q4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R4">
         <v>23.3</v>
@@ -922,69 +978,69 @@
         <v>340</v>
       </c>
       <c r="U4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V4">
         <v>-2.1</v>
       </c>
       <c r="W4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="18.75" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="D5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="H5" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="M5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="O5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P5">
         <v>11</v>
       </c>
       <c r="Q5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S5">
         <v>11.9</v>
@@ -993,13 +1049,201 @@
         <v>105</v>
       </c>
       <c r="U5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V5">
         <v>-1.1000000000000001</v>
       </c>
       <c r="W5" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" t="s">
+        <v>73</v>
+      </c>
+      <c r="O6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N8" t="s">
+        <v>73</v>
+      </c>
+      <c r="O8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/数据.xlsx
+++ b/dataset/数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSBR\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74681194-51CF-4DC7-B10D-517C7686C11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499BDFDD-0DCE-41F0-94A7-6E99A9DD03B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="97">
   <si>
     <t>样本ID</t>
   </si>
@@ -67,30 +67,12 @@
     <t>DOI_SI</t>
   </si>
   <si>
-    <t>SSBR-001</t>
-  </si>
-  <si>
     <t>绿色轮胎胎面胶</t>
   </si>
   <si>
-    <t>无（空白未官能化 SSBR）</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>文献 Fig.1 (A/B/C) 基础 SSBR 核磁谱图</t>
-  </si>
-  <si>
-    <t>文献 Fig.5 (A) 空白复合材料 TEM 微相分离图</t>
-  </si>
-  <si>
-    <t>文献 Fig.8 (A) 空白复合材料应力 - 应变曲线</t>
-  </si>
-  <si>
-    <t>文献 Fig.2 基础 SSBR 生胶 DSC 谱图</t>
-  </si>
-  <si>
     <t>Gao W ,Lu J ,Song W , et al.Interfacial interaction modes construction of various functional SSBR-silica towards high filler dispersion and excellent composites performances[J].RSC Advances,2019,9(33):18888-18897.</t>
   </si>
   <si>
@@ -190,15 +172,9 @@
     <t>文献 Fig.2 SSBR-g-MPTES 生胶 DSC 谱图</t>
   </si>
   <si>
-    <t>SSBR-005</t>
-  </si>
-  <si>
     <t>绿色轮胎/硅胶复合材料</t>
   </si>
   <si>
-    <t>0 wt%</t>
-  </si>
-  <si>
     <t>文献 Fig.1 NMR谱图</t>
   </si>
   <si>
@@ -241,9 +217,6 @@
     <t>9.60 wt%</t>
   </si>
   <si>
-    <t>SSBR-009</t>
-  </si>
-  <si>
     <t>轮胎、密封件与减震器</t>
   </si>
   <si>
@@ -301,13 +274,7 @@
     <t>6.09 wt%</t>
   </si>
   <si>
-    <t>SSBR-013</t>
-  </si>
-  <si>
     <t>文献 Fig.1 ¹H NMR谱图</t>
-  </si>
-  <si>
-    <t>文献 Fig.9(b) TEM图</t>
   </si>
   <si>
     <t>文献 Fig.12 tan δ曲线</t>
@@ -417,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -432,9 +399,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -759,27 +723,27 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.7265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.26953125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="18.26953125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.26953125" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.7265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="52" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="52.26953125" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="41.7265625" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="230.54296875" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="29" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="18.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.26953125" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="52" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="52.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="41.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="230.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="29" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.54296875" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.54296875" style="9" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.54296875" style="10" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -840,821 +804,628 @@
     </row>
     <row r="2" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="7"/>
+      <c r="P2" s="6"/>
       <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="V2" s="8"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="7"/>
+      <c r="V2" s="6"/>
     </row>
     <row r="3" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H3" s="2">
-        <v>3.5999999999999997E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="7"/>
-      <c r="R3" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="P3" s="6"/>
+      <c r="R3" s="6"/>
       <c r="S3" s="7"/>
-      <c r="T3" s="8"/>
-      <c r="V3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="V3" s="6"/>
     </row>
     <row r="4" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H4" s="2">
-        <v>8.6999999999999994E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="P4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="V4" s="7"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="7"/>
+      <c r="V4" s="6"/>
     </row>
-    <row r="5" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="2">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="8"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="8"/>
-      <c r="V5" s="7"/>
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="O6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="N8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="O8" s="1" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="J11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="L11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="O11" s="1" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="J13" s="1" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="O13" s="1" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/数据.xlsx
+++ b/dataset/数据.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="70">
   <si>
     <t>样本ID</t>
   </si>
@@ -46,6 +46,9 @@
     <t>接枝反应基团</t>
   </si>
   <si>
+    <t>接枝反应基团SMILES</t>
+  </si>
+  <si>
     <t>核心官能团 SMILES</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
   </si>
   <si>
     <t>巯基</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
   <si>
     <t>O</t>
@@ -613,7 +619,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="8.719285714285713" customWidth="1" bestFit="1"/>
@@ -626,12 +632,12 @@
     <col min="8" max="8" style="9" width="36.29071428571429" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="9" width="36.71928571428572" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="9" width="52.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="9" width="52.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="10" width="52.29071428571429" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="9" width="41.71928571428572" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="9" width="16.862142857142857" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="9" width="29.005" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="9" width="29.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="10" width="52.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="9" width="52.14785714285715" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="10" width="16.290714285714284" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -639,6 +645,7 @@
     <col min="21" max="21" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -672,7 +679,7 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -687,10 +694,10 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
@@ -702,331 +709,349 @@
       <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="Q2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="R2" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="S2" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="T2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="R4" s="6"/>
-      <c r="S4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T4" s="7"/>
-      <c r="U4" s="2" t="s">
+      <c r="P4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S4" s="6"/>
+      <c r="T4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="V4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="W4" s="2" t="s">
+      <c r="U4" s="7"/>
+      <c r="V4" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2" t="s">
+      <c r="S5" s="2"/>
+      <c r="T5" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -1040,12 +1065,12 @@
       <c r="H7" s="8"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="K7" s="2"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="2"/>
+      <c r="P7" s="1"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
@@ -1053,6 +1078,7 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1"/>
@@ -1065,12 +1091,12 @@
       <c r="H8" s="8"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="K8" s="2"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="2"/>
+      <c r="P8" s="1"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
@@ -1078,6 +1104,7 @@
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
@@ -1090,12 +1117,12 @@
       <c r="H9" s="8"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+      <c r="K9" s="2"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="2"/>
+      <c r="P9" s="1"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
@@ -1103,6 +1130,7 @@
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
@@ -1115,12 +1143,12 @@
       <c r="H10" s="8"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="K10" s="2"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="2"/>
+      <c r="P10" s="1"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
@@ -1128,6 +1156,7 @@
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1"/>
@@ -1140,12 +1169,12 @@
       <c r="H11" s="8"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="K11" s="2"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="2"/>
+      <c r="P11" s="1"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -1153,6 +1182,7 @@
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1"/>
@@ -1165,12 +1195,12 @@
       <c r="H12" s="8"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="K12" s="2"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="2"/>
+      <c r="P12" s="1"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
@@ -1178,6 +1208,7 @@
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1"/>
@@ -1190,12 +1221,12 @@
       <c r="H13" s="8"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="2"/>
+      <c r="P13" s="1"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
@@ -1203,6 +1234,7 @@
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1"/>
@@ -1215,12 +1247,12 @@
       <c r="H14" s="8"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="K14" s="2"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="2"/>
+      <c r="P14" s="1"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
@@ -1228,6 +1260,7 @@
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataset/数据.xlsx
+++ b/dataset/数据.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="785">
   <si>
     <t>样本ID</t>
   </si>
@@ -1712,6 +1712,663 @@
   </si>
   <si>
     <t>10.4028/www.scientific.net/AMR.11-12.657</t>
+  </si>
+  <si>
+    <t>SSBR-083</t>
+  </si>
+  <si>
+    <t>绿色轮胎、白炭黑/EBR 纳米复合材料</t>
+  </si>
+  <si>
+    <t>文献 Fig.11 应力-应变曲线</t>
+  </si>
+  <si>
+    <t>Hui J, Liu L, Zhang Y, et al. Structure and performance of silica/functionalized solution-polymerized styrene butadiene rubber/epoxidized butadiene rubber nanocomposites[J]. Polymer, 2024, 294: 126682.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polymer.2024.126682</t>
+  </si>
+  <si>
+    <t>SSBR-084</t>
+  </si>
+  <si>
+    <t>轮胎、可逆网络、功能化接枝</t>
+  </si>
+  <si>
+    <t>腈氧化物 (CNO-py/CNO-COOH)</t>
+  </si>
+  <si>
+    <t>c1cc[n+]cc1C=N[O-].OC(=O)c1ccccc1C=N[O-]</t>
+  </si>
+  <si>
+    <t>吡啶基/羧基</t>
+  </si>
+  <si>
+    <t>1.9-16.8</t>
+  </si>
+  <si>
+    <t>c1cc[n+]cc1C=N[O-]-161000-10-41-C=C--16.8%</t>
+  </si>
+  <si>
+    <t>Jiang L, Manai D, Kawasaki S, et al. Ionic functionalization of poly(styrene-co-butadiene) via catalyst-free click reactions with acid and base-tethered nitrile N-oxides[J]. European Polymer Journal, 2025, 223: 113653.</t>
+  </si>
+  <si>
+    <t>10.1016/j.europolj.2024.113653</t>
+  </si>
+  <si>
+    <t>SSBR-085</t>
+  </si>
+  <si>
+    <t>橡胶混炼加工、内混机磨损研究</t>
+  </si>
+  <si>
+    <t>石墨烯润滑剂</t>
+  </si>
+  <si>
+    <t>Han D, Liu C, Wang L, et al. Investigation of NR, BR, and SBR composite material properties and internal mixer Wear under various lubricating oil media during mixing process[J]. Surface &amp; Coatings Technology, 2024, 480: 130611.</t>
+  </si>
+  <si>
+    <t>10.1016/j.surfcoat.2024.130611</t>
+  </si>
+  <si>
+    <t>SSBR-086</t>
+  </si>
+  <si>
+    <t>高性能绿色轮胎</t>
+  </si>
+  <si>
+    <t>胺封端 TBIR</t>
+  </si>
+  <si>
+    <t>文献 Table 3</t>
+  </si>
+  <si>
+    <t>Luo S, Dong K, Wang S, et al. Synergistic enhancement of magic triangle properties of PC tread stocks modified by amine-capped trans-1,4-poly (butadiene-co-isoprene)[J]. Composites Science and Technology, 2024, 258: 110899.</t>
+  </si>
+  <si>
+    <t>10.1016/j.compscitech.2024.110899</t>
+  </si>
+  <si>
+    <t>SSBR-087</t>
+  </si>
+  <si>
+    <t>半潜式平台垂荡性能减缓</t>
+  </si>
+  <si>
+    <t>Emami A, Pourjafari N, Parghi A. Effect of porous SBR composites on mitigating the heave motion response of a semi-submersible platform[J]. Ocean Engineering, 2024, 295: 116856.</t>
+  </si>
+  <si>
+    <t>10.1016/j.oceaneng.2024.116856</t>
+  </si>
+  <si>
+    <t>SSBR-088</t>
+  </si>
+  <si>
+    <t>H2O2 + 催化剂 CPC-PW4O16</t>
+  </si>
+  <si>
+    <t>-25-57-C=C-C1OC1-8%</t>
+  </si>
+  <si>
+    <t>Liu S, Liu L, Wu Q, et al. Silica reinforced epoxidized solution-polymerized styrene butadiene rubber and epoxidized polybutadiene rubber nanocomposite as green tire tread[J]. Polymer, 2023, 281: 126082.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polymer.2023.126082</t>
+  </si>
+  <si>
+    <t>SSBR-089</t>
+  </si>
+  <si>
+    <t>绿色轮胎胎面胶性能增强</t>
+  </si>
+  <si>
+    <t>Hui J, Liu L, Zhao B, et al. Performance enhancement of silica reinforced functionalized solution-polymerized styrene butadiene rubber/epoxidized natural rubber nanocomposites as green tyre treads[J]. Polymer, 2025, 325: 128308.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polymer.2025.128308</t>
+  </si>
+  <si>
+    <t>SSBR-090</t>
+  </si>
+  <si>
+    <t>水下吸声材料、非共价键网络</t>
+  </si>
+  <si>
+    <t>UPy-NCO</t>
+  </si>
+  <si>
+    <t>CC1=CC(=O)NC(=N1)NCNC(=O)NCCCCCC</t>
+  </si>
+  <si>
+    <t>羟基 (接枝于后修饰后的HSBR)</t>
+  </si>
+  <si>
+    <t>[nH]1c(NC(=O)N)nc(C)cc1=O</t>
+  </si>
+  <si>
+    <t>脲基嘧啶酮</t>
+  </si>
+  <si>
+    <t>CC1=CC(=O)NC(=N1)NCNC(=O)NCCCCCC---O-[nH]1c(NC(=O)N)nc(C)cc1=O-</t>
+  </si>
+  <si>
+    <t>Wang W, Liao M. Enhancing underwater sound absorption properties of solution-polymerized styrene-butadiene rubber through hydrogen bonding interactions[J]. Polymer, 2025, 334: 128729.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polymer.2024.128729</t>
+  </si>
+  <si>
+    <t>SSBR-091</t>
+  </si>
+  <si>
+    <t>绿色轮胎、天然橡胶网络研究</t>
+  </si>
+  <si>
+    <t>Xiao Y, Li B, Diao P, et al. Raw rubber network of acid-free natural rubber and its application with solution-polymerized styrene butadiene rubber in green tires[J]. Polymer Testing, 2024, 140: 108605.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polytest.2024.108605</t>
+  </si>
+  <si>
+    <t>SSBR-092</t>
+  </si>
+  <si>
+    <t>橡胶增强、炭黑分散</t>
+  </si>
+  <si>
+    <t>三嗪基石墨炔 (TGDY)</t>
+  </si>
+  <si>
+    <t>三嗪基</t>
+  </si>
+  <si>
+    <t>文献 Fig.3 硫化曲线</t>
+  </si>
+  <si>
+    <t>Sun C, Fan C, Kan X, et al. Enhanced cross-linking performances and carbon black (CB) dispersion in solution styrene butadiene rubber (SSBR) filled with triazine-based graphdiyne (TGDY)[J]. Composites Science and Technology, 2022, 223: 109438.</t>
+  </si>
+  <si>
+    <t>10.1016/j.compscitech.2022.109438</t>
+  </si>
+  <si>
+    <t>SSBR-093</t>
+  </si>
+  <si>
+    <t>节能轮胎、低滚阻复合材料</t>
+  </si>
+  <si>
+    <t>硫醇官能化氧化石墨烯</t>
+  </si>
+  <si>
+    <t>硫醇基</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 SEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.8 损耗因子</t>
+  </si>
+  <si>
+    <t>Zhang R, Li J, Xu Z, et al. Achieving strong chemical interface and superior energy-saving capability at the crosslinks of rubber composites containing graphene oxide using thiol-vinyl click chemistry[J]. Composites Science and Technology, 2023, 233: 109907.</t>
+  </si>
+  <si>
+    <t>10.1016/j.compscitech.2022.109907</t>
+  </si>
+  <si>
+    <t>SSBR-094</t>
+  </si>
+  <si>
+    <t>绿色轮胎、天然橡胶 masterbatch</t>
+  </si>
+  <si>
+    <t>文献 Fig.4 AFM图</t>
+  </si>
+  <si>
+    <t>Xiao Y, Ge Y, Wang L, et al. Enhanced magic triangle performance of green tire compounds by acid-free natural rubber/silica masterbatch with flash evaporation process[J]. Industrial Crops &amp; Products, 2025, 236: 122017.</t>
+  </si>
+  <si>
+    <t>10.1016/j.indcrop.2025.122017</t>
+  </si>
+  <si>
+    <t>SSBR-095</t>
+  </si>
+  <si>
+    <t>21.0</t>
+  </si>
+  <si>
+    <t>63.0</t>
+  </si>
+  <si>
+    <t>绿色轮胎、功能化 SSBR 合成</t>
+  </si>
+  <si>
+    <t>三苯基硅烷 (TPS)</t>
+  </si>
+  <si>
+    <t>[SiH](c1ccccc1)(c2ccccc2)c3ccccc3</t>
+  </si>
+  <si>
+    <t>硅氢基</t>
+  </si>
+  <si>
+    <t>[SiH]</t>
+  </si>
+  <si>
+    <t>[Si](c1ccccc1)(c2ccccc2)c3ccccc3</t>
+  </si>
+  <si>
+    <t>三苯基硅基</t>
+  </si>
+  <si>
+    <t>-SiPh3</t>
+  </si>
+  <si>
+    <t>3.6-11.2</t>
+  </si>
+  <si>
+    <t>[SiH](c1ccccc1)(c2ccccc2)c3ccccc3-100000-21.0-63.0-[SiH]-[Si](c1ccccc1)(c2ccccc2)c3ccccc3-11.2%</t>
+  </si>
+  <si>
+    <t>文献 Fig.8 (TEM)</t>
+  </si>
+  <si>
+    <t>文献 Fig.9 (DMA)</t>
+  </si>
+  <si>
+    <t>Li H, Liu L, Zhang Y, et al. Hydrosilylation of solution-polymerized styrene-butadiene rubber with triphenylsilane[J]. Reactive and Functional Polymers, 2025, 213: 106258.</t>
+  </si>
+  <si>
+    <t>10.1016/j.reactfunctpolym.2024.106258</t>
+  </si>
+  <si>
+    <t>SSBR-096</t>
+  </si>
+  <si>
+    <t>高分子性能预测、机器学习</t>
+  </si>
+  <si>
+    <t>Zhan S, Huang W, Dong C, et al. Predicting glass transition temperature of polymers by combining molecular dynamics simulations and machine learning techniques[J]. Materials Today Communications, 2024, 40: 110181.</t>
+  </si>
+  <si>
+    <t>10.1016/j.mtcomm.2024.110181</t>
+  </si>
+  <si>
+    <t>SSBR-097</t>
+  </si>
+  <si>
+    <t>轮胎工业、树脂/橡胶相容性研究</t>
+  </si>
+  <si>
+    <t>烃类树脂</t>
+  </si>
+  <si>
+    <t>Yu L, Colvin H, Rosmus J J, et al. COMPATIBILITY STUDY OF HYDROCARBON RESINS WITH RUBBER COMPOUNDS FOR TIRE APPLICATIONS[J]. Rubber Chemistry and Technology, 2024, 97(2): 145-161.</t>
+  </si>
+  <si>
+    <t>10.5254/RCT-D-23-00043</t>
+  </si>
+  <si>
+    <t>SSBR-098</t>
+  </si>
+  <si>
+    <t>橡胶增强、白炭黑改性</t>
+  </si>
+  <si>
+    <t>文献 Fig.5 (SEM)</t>
+  </si>
+  <si>
+    <t>文献 Fig.11 (应力-应变)</t>
+  </si>
+  <si>
+    <t>Tian Q, Tang Y, Lv X, et al. Double-layer modified silica with potential reinforcement for solution polymerized styrene-butadiene rubber/butadiene rubber composite[J]. Journal of Applied Polymer Science, 2022, 139(9): 51959.</t>
+  </si>
+  <si>
+    <t>10.1002/app.51959</t>
+  </si>
+  <si>
+    <t>SSBR-099</t>
+  </si>
+  <si>
+    <t>绿色轮胎、抗湿滑改性</t>
+  </si>
+  <si>
+    <t>甲酸 + 过氧化氢</t>
+  </si>
+  <si>
+    <t>C(=O)O.OO</t>
+  </si>
+  <si>
+    <t>C(=O)O--25--C=C-C1OC1-10.09%</t>
+  </si>
+  <si>
+    <t>文献 Fig.7 (DMA)</t>
+  </si>
+  <si>
+    <t>Chen J, Li C, Chen X, et al. Insights into the preparation and performance of SiO2@graphene oxide/epoxidized solution-polymerized styrene butadiene rubber composites through experiments and molecular simulations[J]. Journal of Applied Polymer Science, 2022, 139(26): 52432.</t>
+  </si>
+  <si>
+    <t>10.1002/app.52432</t>
+  </si>
+  <si>
+    <t>SSBR-100</t>
+  </si>
+  <si>
+    <t>绿色轮胎、生物基复合材料</t>
+  </si>
+  <si>
+    <t>环氧化天然橡胶 (ENR)</t>
+  </si>
+  <si>
+    <t>文献 Fig.8 (DMA)</t>
+  </si>
+  <si>
+    <t>Wang Z, Li Y, Song W, et al. Performance enhancement of bio-based rubber composites using epoxidized natural rubber for silica without carbon emissions and volatile organic compounds[J]. Journal of Applied Polymer Science, 2022, 139.</t>
+  </si>
+  <si>
+    <t>10.1002/app.52682</t>
+  </si>
+  <si>
+    <t>SSBR-101</t>
+  </si>
+  <si>
+    <t>绿色轮胎、白炭黑界面工程</t>
+  </si>
+  <si>
+    <t>环氧化 SSBR (ESSBR)</t>
+  </si>
+  <si>
+    <t>文献 Fig.3 (TEM)</t>
+  </si>
+  <si>
+    <t>文献 Fig.6 (力学)</t>
+  </si>
+  <si>
+    <t>Chen H, Li H, Zhao W, et al. Strong Interface and High Dispersion of Silica Engineered by Polydopamine and Epoxidized Elastomer[J]. Journal of Applied Polymer Science, 2026.</t>
+  </si>
+  <si>
+    <t>10.1002/app.70577</t>
+  </si>
+  <si>
+    <t>SSBR-102</t>
+  </si>
+  <si>
+    <t>高填充白炭黑复合材料研究</t>
+  </si>
+  <si>
+    <t>文献 Fig.6 (应力-应变)</t>
+  </si>
+  <si>
+    <t>Lu Y, Zhang G, Zhang Y, et al. Effect of Silica Content on the Properties of Highly Filled Silica/SSBR Composites[J]. Journal of Applied Polymer Science, 2026, 143.</t>
+  </si>
+  <si>
+    <t>10.1002/app.70405</t>
+  </si>
+  <si>
+    <t>SSBR-103</t>
+  </si>
+  <si>
+    <t>阴离子聚合动力学研究</t>
+  </si>
+  <si>
+    <t>Bronskaya V, Manuyko G, Balzamov D, et al. Copolymerization of butadiene and styrene under the influence of n-butyllithium[J]. Arabian Journal of Chemistry, 2023, 16(11): 105205.</t>
+  </si>
+  <si>
+    <t>10.1016/j.arabjc.2023.105205</t>
+  </si>
+  <si>
+    <t>SSBR-104</t>
+  </si>
+  <si>
+    <t>高阻尼聚氨酯弹性体</t>
+  </si>
+  <si>
+    <t>文献 Fig.5 (DMA)</t>
+  </si>
+  <si>
+    <t>Zhao Y, Shou T, Fu S, et al. Controllable Design and Preparation of Hydroxyl-Terminated Solution-Polymerized Styrene Butadiene for Polyurethane Elastomers with High-Damping Properties[J]. Macromolecular Rapid Communications, 2022, 43(18): 2200366.</t>
+  </si>
+  <si>
+    <t>10.1002/marc.202200366</t>
+  </si>
+  <si>
+    <t>SSBR-105</t>
+  </si>
+  <si>
+    <t>SSBR 力学性能预测、迁移学习</t>
+  </si>
+  <si>
+    <t>文献 Fig.2 TEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 应力-应变曲线</t>
+  </si>
+  <si>
+    <t>Zhan S, Li Z, Zhao H, et al. Transfer Learning for Polymer Mechanics: A Fusion Approach to Bridge Molecular Dynamics Simulations and Experiments in SSBR[J]. Macromolecular Rapid Communications, 2025, 46.</t>
+  </si>
+  <si>
+    <t>10.1002/marc.202500386</t>
+  </si>
+  <si>
+    <t>SSBR-106</t>
+  </si>
+  <si>
+    <t>甲酸 + 过氧化氢 (原位过氧甲酸)</t>
+  </si>
+  <si>
+    <t>C(=O)O.OO--25-57-C=C-C1OC1-12%</t>
+  </si>
+  <si>
+    <t>文献 Fig.7 模量曲线</t>
+  </si>
+  <si>
+    <t>Wu Q, Liu L, Meng J, et al. Microstructure and Performance of Green Tire Tread Based on Epoxidized Solution Polymerized Styrene Butadiene Rubber and Epoxidized Natural Rubber[J]. Industrial &amp; Engineering Chemistry Research, 2023, 62(14): 5582-5593.</t>
+  </si>
+  <si>
+    <t>10.1021/acs.iecr.3c00046</t>
+  </si>
+  <si>
+    <t>SSBR-107</t>
+  </si>
+  <si>
+    <t>绿色轮胎、白炭黑增强</t>
+  </si>
+  <si>
+    <t>C3N4/SiO2 纳米杂化材料</t>
+  </si>
+  <si>
+    <t>Wang Z, Wang H, Shen X, et al. In situ assembled C3N4/SiO2 nanohybrids for high comprehensive performance solution polymerized styrene-butadiene rubber/butadiene rubber[J]. Polymer Composites, 2022, 43.</t>
+  </si>
+  <si>
+    <t>10.1002/pc.26994</t>
+  </si>
+  <si>
+    <t>SSBR-108</t>
+  </si>
+  <si>
+    <t>橡胶增强、填料改性</t>
+  </si>
+  <si>
+    <t>硅氧烷改性氧化石墨烯 (rGO-g-SiO2)</t>
+  </si>
+  <si>
+    <t>文献 Fig.9 TEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.9 动态力学谱图</t>
+  </si>
+  <si>
+    <t>Zhang H, Cai F, Luo Y, et al. Grafting silica onto reduced graphene oxide via hydrosilylation for comprehensive rubber applications: Molecular simulation and experimental study[J]. Polymer Composites, 2022, 43.</t>
+  </si>
+  <si>
+    <t>10.1002/pc.26830</t>
+  </si>
+  <si>
+    <t>SSBR-109</t>
+  </si>
+  <si>
+    <t>绿色轮胎胎面胶、高性能复合材料</t>
+  </si>
+  <si>
+    <t>3-氨基丙基三乙氧基硅烷 (APTES)</t>
+  </si>
+  <si>
+    <t>NCCCN[Si](OCC)(OCC)OCC</t>
+  </si>
+  <si>
+    <t>环氧基 (接枝于ESSBR)</t>
+  </si>
+  <si>
+    <t>% (ESSBR)</t>
+  </si>
+  <si>
+    <t>NCCCN[Si](OCC)(OCC)OCC--25-57-C1OC1--12%</t>
+  </si>
+  <si>
+    <t>Hui J, Liu L, Yu Z, et al. Silane coupling agent 3‐aminopropyltriethoxysilane modified silica/epoxidized solution-polymerized styrene butadiene rubber nanocomposites[J]. Polymer Composites, 2023, 44.</t>
+  </si>
+  <si>
+    <t>10.1002/pc.27610</t>
+  </si>
+  <si>
+    <t>SSBR-110</t>
+  </si>
+  <si>
+    <t>导热橡胶复合材料</t>
+  </si>
+  <si>
+    <t>Cheng Y, Wang Q, Fang H. Experimental study on the continuous preparation of high‐performance thermal conductivity CNTs/EG/SSBR composite based on the shear and elongation flow fields with the assistance of the silanization reaction[J]. Polymer Composites, 2024, 45.</t>
+  </si>
+  <si>
+    <t>10.1002/pc.28697</t>
+  </si>
+  <si>
+    <t>SSBR-111</t>
+  </si>
+  <si>
+    <t>绿色轮胎、高性能复合材料</t>
+  </si>
+  <si>
+    <t>三乙氧基硅烷 (TES)</t>
+  </si>
+  <si>
+    <t>O(CC)[SiH](OCC)OCC</t>
+  </si>
+  <si>
+    <t>碳碳双键 (硅氢加成)</t>
+  </si>
+  <si>
+    <t>O(CC)[SiH](OCC)OCC---C=C-[Si](OCC)(OCC)OCC-10mol%</t>
+  </si>
+  <si>
+    <t>文献 Fig.2 ¹H NMR</t>
+  </si>
+  <si>
+    <t>文献 Fig.5 动态力学谱图</t>
+  </si>
+  <si>
+    <t>Li H, Liu L, Zhang Y, et al. Nanocomposites of Triethoxysilane Functionalized Solution Polymerized Styrene‐Butadiene Rubber by Hydrosilylation as High‐Performance Green Tire[J]. Polymer Composites, 2025, 47: 3879-3888.</t>
+  </si>
+  <si>
+    <t>10.1002/pc.70402</t>
+  </si>
+  <si>
+    <t>SSBR-112</t>
+  </si>
+  <si>
+    <t>环保型橡胶增塑剂研究</t>
+  </si>
+  <si>
+    <t>液体聚丁二烯 (LPB)</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 动态力学谱图</t>
+  </si>
+  <si>
+    <t>Liu Z Y, Han L, Wang R J, et al. Influence of liquid polybutadiene on crosslinking network and mechanical properties of SSBR/BR[J]. Polymer Engineering &amp; Science, 2022, 62.</t>
+  </si>
+  <si>
+    <t>10.1002/pen.25931</t>
+  </si>
+  <si>
+    <t>SSBR-113</t>
+  </si>
+  <si>
+    <t>动力电池极片压延橡胶辊</t>
+  </si>
+  <si>
+    <t>He H, Xing Y, Yan R, et al. Research on the influencing factors of hysteresis heat of rubber roller in battery pole piece calendering[J]. Polymer Engineering &amp; Science, 2024, 64(3): 1133-1144.</t>
+  </si>
+  <si>
+    <t>10.1002/pen.26601</t>
+  </si>
+  <si>
+    <t>SSBR-114</t>
+  </si>
+  <si>
+    <t>绿色轮胎、高分散白炭黑</t>
+  </si>
+  <si>
+    <t>乙烯基三甲氧基硅烷 (VTMS)</t>
+  </si>
+  <si>
+    <t>CO[Si](OC)(OC)C=C</t>
+  </si>
+  <si>
+    <t>碳碳双键 (烯烃复分解)</t>
+  </si>
+  <si>
+    <t>三甲氧基硅烷基</t>
+  </si>
+  <si>
+    <t>CO[Si](OC)(OC)C=C--19-10-C=C-[Si](OC)(OC)OC-</t>
+  </si>
+  <si>
+    <t>Liu J, Lyu J, Shen M, et al. Using olefin metathesis reaction to modify solution polymerized styrene-butadiene rubber (SSBR) by for a more stable “green tire”[J]. Journal of Polymer Research, 2023, 30(3): 90.</t>
+  </si>
+  <si>
+    <t>10.1007/s10965-023-03446-7</t>
+  </si>
+  <si>
+    <t>SSBR-115</t>
+  </si>
+  <si>
+    <t>绿色轮胎胎面胶、高分散白炭黑</t>
+  </si>
+  <si>
+    <t>C(=O)O.OO--25-57-C=C-C1OC1-13.8mol%</t>
+  </si>
+  <si>
+    <t>文献 Fig.10 (应力-应变)</t>
+  </si>
+  <si>
+    <t>Yuan J, Liu L, Wang X, et al. Structure and Performance of Silica-Grafted Epoxidized Solution-Polymerized Styrene-Butadiene Nanocomposites[J]. Industrial &amp; Engineering Chemistry Research, 2022, 61(8): 3031-3043.</t>
+  </si>
+  <si>
+    <t>10.1021/acs.iecr.1c04519</t>
+  </si>
+  <si>
+    <t>SSBR-116</t>
+  </si>
+  <si>
+    <t>绿色轮胎、白炭黑分散增强</t>
+  </si>
+  <si>
+    <t>m-氯过氧苯甲酸 (mCPBA)</t>
+  </si>
+  <si>
+    <t>Clc1cccc(C(=O)OO)c1--25---C=C-C1OC1-</t>
+  </si>
+  <si>
+    <t>文献 Fig.4 SEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.11 应力-应变</t>
+  </si>
+  <si>
+    <t>Xiao T, Wan L, Dong F, et al. Enhancing silica dispersion and interfacial interaction in styrene butadiene/silica rubber composites by using epoxidized styrene butadiene rubber as interfacial compatibilizer[J]. Vinyl and Additive Technology, 2023, 29(4): 742-751.</t>
+  </si>
+  <si>
+    <t>10.1002/vnl.22007</t>
   </si>
 </sst>
 </file>
@@ -1729,7 +2386,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1782,7 +2439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1793,10 +2450,16 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -2110,33 +2773,33 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:X83"/>
+  <dimension ref="A1:X117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="7" width="64.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="7" width="22.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="9" width="64.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="9" width="22.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -2588,8 +3251,8 @@
       <c r="D7" s="5">
         <v>23.5</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="3" t="s">
         <v>71</v>
       </c>
@@ -2600,7 +3263,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="6"/>
+      <c r="O7" s="7"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
         <v>72</v>
@@ -2634,8 +3297,8 @@
       <c r="D8" s="5">
         <v>23.5</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="3" t="s">
         <v>78</v>
       </c>
@@ -2646,7 +3309,7 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="6"/>
+      <c r="O8" s="7"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
         <v>72</v>
@@ -2677,9 +3340,9 @@
       <c r="C9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="3" t="s">
         <v>84</v>
       </c>
@@ -2690,7 +3353,7 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="6"/>
+      <c r="O9" s="7"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
         <v>85</v>
@@ -2721,9 +3384,9 @@
       <c r="C10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="3" t="s">
         <v>27</v>
       </c>
@@ -2734,7 +3397,7 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="6"/>
+      <c r="O10" s="7"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
         <v>85</v>
@@ -2765,9 +3428,9 @@
       <c r="C11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="3" t="s">
         <v>96</v>
       </c>
@@ -2778,7 +3441,7 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="6"/>
+      <c r="O11" s="7"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
         <v>97</v>
@@ -2810,8 +3473,8 @@
       <c r="D12" s="5">
         <v>25.37</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="3" t="s">
         <v>102</v>
       </c>
@@ -2822,7 +3485,7 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="6"/>
+      <c r="O12" s="7"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
         <v>103</v>
@@ -2872,7 +3535,7 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="6"/>
+      <c r="O13" s="7"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
         <v>110</v>
@@ -2913,7 +3576,7 @@
       <c r="E14" s="4">
         <v>57</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="3" t="s">
         <v>117</v>
       </c>
@@ -2924,7 +3587,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="6"/>
+      <c r="O14" s="7"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
         <v>118</v>
@@ -2959,7 +3622,7 @@
       <c r="E15" s="4">
         <v>45</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="7"/>
       <c r="G15" s="3" t="s">
         <v>117</v>
       </c>
@@ -2970,7 +3633,7 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="6"/>
+      <c r="O15" s="7"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
         <v>123</v>
@@ -3002,7 +3665,7 @@
       <c r="D16" s="5">
         <v>20.1</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="4">
         <v>196000</v>
       </c>
@@ -3066,7 +3729,7 @@
       <c r="D17" s="5">
         <v>20.1</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="4">
         <v>196000</v>
       </c>
@@ -3128,8 +3791,8 @@
       <c r="D18" s="5">
         <v>23.5</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="3" t="s">
         <v>147</v>
       </c>
@@ -3154,7 +3817,7 @@
       <c r="N18" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="O18" s="6"/>
+      <c r="O18" s="7"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -3183,9 +3846,9 @@
       <c r="C19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="3" t="s">
         <v>157</v>
       </c>
@@ -3202,7 +3865,7 @@
       <c r="N19" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="O19" s="6"/>
+      <c r="O19" s="7"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3" t="s">
@@ -3232,7 +3895,7 @@
       <c r="D20" s="5">
         <v>20.1</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="7"/>
       <c r="F20" s="4">
         <v>196000</v>
       </c>
@@ -3294,8 +3957,8 @@
       <c r="D21" s="5">
         <v>23.5</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="3" t="s">
         <v>147</v>
       </c>
@@ -3320,7 +3983,7 @@
       <c r="N21" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="O21" s="6"/>
+      <c r="O21" s="7"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3" t="s">
         <v>167</v>
@@ -3351,9 +4014,9 @@
       <c r="C22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="3" t="s">
         <v>157</v>
       </c>
@@ -3370,7 +4033,7 @@
       <c r="N22" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="O22" s="6"/>
+      <c r="O22" s="7"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3" t="s">
@@ -3400,7 +4063,7 @@
       <c r="D23" s="4">
         <v>24</v>
       </c>
-      <c r="E23" s="6"/>
+      <c r="E23" s="7"/>
       <c r="F23" s="4">
         <v>168000</v>
       </c>
@@ -3524,8 +4187,8 @@
       <c r="D25" s="4">
         <v>27</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
       <c r="G25" s="3" t="s">
         <v>179</v>
       </c>
@@ -3589,7 +4252,7 @@
       <c r="E26" s="4">
         <v>26</v>
       </c>
-      <c r="F26" s="6"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="3" t="s">
         <v>198</v>
       </c>
@@ -3606,7 +4269,7 @@
         <v>201</v>
       </c>
       <c r="N26" s="3"/>
-      <c r="O26" s="6"/>
+      <c r="O26" s="7"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
@@ -3633,8 +4296,8 @@
       <c r="C27" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
       <c r="F27" s="4">
         <v>150000</v>
       </c>
@@ -3654,7 +4317,7 @@
         <v>208</v>
       </c>
       <c r="N27" s="3"/>
-      <c r="O27" s="6"/>
+      <c r="O27" s="7"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
@@ -3681,9 +4344,9 @@
       <c r="C28" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
       <c r="G28" s="3" t="s">
         <v>212</v>
       </c>
@@ -3694,7 +4357,7 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
-      <c r="O28" s="6"/>
+      <c r="O28" s="7"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3" t="s">
@@ -3723,9 +4386,9 @@
       <c r="C29" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
       <c r="G29" s="3" t="s">
         <v>216</v>
       </c>
@@ -3736,7 +4399,7 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
-      <c r="O29" s="6"/>
+      <c r="O29" s="7"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -3761,9 +4424,9 @@
       <c r="C30" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
       <c r="G30" s="3" t="s">
         <v>216</v>
       </c>
@@ -3774,7 +4437,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
-      <c r="O30" s="6"/>
+      <c r="O30" s="7"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -3802,7 +4465,7 @@
       <c r="D31" s="4">
         <v>21</v>
       </c>
-      <c r="E31" s="6"/>
+      <c r="E31" s="7"/>
       <c r="F31" s="4">
         <v>206600</v>
       </c>
@@ -3872,7 +4535,7 @@
       <c r="D32" s="5">
         <v>20.7</v>
       </c>
-      <c r="E32" s="6"/>
+      <c r="E32" s="7"/>
       <c r="F32" s="4">
         <v>214700</v>
       </c>
@@ -3938,7 +4601,7 @@
       <c r="D33" s="5">
         <v>25.3</v>
       </c>
-      <c r="E33" s="6"/>
+      <c r="E33" s="7"/>
       <c r="F33" s="4">
         <v>192000</v>
       </c>
@@ -3952,7 +4615,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
-      <c r="O33" s="6"/>
+      <c r="O33" s="7"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
@@ -3985,9 +4648,9 @@
       <c r="C34" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="3" t="s">
         <v>243</v>
       </c>
@@ -4008,7 +4671,7 @@
         <v>248</v>
       </c>
       <c r="N34" s="3"/>
-      <c r="O34" s="6"/>
+      <c r="O34" s="7"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3" t="s">
@@ -4039,8 +4702,8 @@
       <c r="C35" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
       <c r="F35" s="4">
         <v>160200</v>
       </c>
@@ -4111,7 +4774,7 @@
       <c r="E36" s="4">
         <v>50</v>
       </c>
-      <c r="F36" s="6"/>
+      <c r="F36" s="7"/>
       <c r="G36" s="3" t="s">
         <v>263</v>
       </c>
@@ -4122,7 +4785,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
-      <c r="O36" s="6"/>
+      <c r="O36" s="7"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
@@ -4157,7 +4820,7 @@
       <c r="E37" s="4">
         <v>50</v>
       </c>
-      <c r="F37" s="6"/>
+      <c r="F37" s="7"/>
       <c r="G37" s="3" t="s">
         <v>269</v>
       </c>
@@ -4172,7 +4835,7 @@
         <v>271</v>
       </c>
       <c r="N37" s="3"/>
-      <c r="O37" s="6"/>
+      <c r="O37" s="7"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
@@ -4207,7 +4870,7 @@
       <c r="E38" s="4">
         <v>50</v>
       </c>
-      <c r="F38" s="6"/>
+      <c r="F38" s="7"/>
       <c r="G38" s="3" t="s">
         <v>276</v>
       </c>
@@ -4218,7 +4881,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
-      <c r="O38" s="6"/>
+      <c r="O38" s="7"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -4253,7 +4916,7 @@
       <c r="E39" s="4">
         <v>50</v>
       </c>
-      <c r="F39" s="6"/>
+      <c r="F39" s="7"/>
       <c r="G39" s="3" t="s">
         <v>281</v>
       </c>
@@ -4274,7 +4937,7 @@
         <v>284</v>
       </c>
       <c r="N39" s="3"/>
-      <c r="O39" s="6"/>
+      <c r="O39" s="7"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
@@ -4307,7 +4970,7 @@
       <c r="E40" s="4">
         <v>50</v>
       </c>
-      <c r="F40" s="6"/>
+      <c r="F40" s="7"/>
       <c r="G40" s="3" t="s">
         <v>289</v>
       </c>
@@ -4318,7 +4981,7 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-      <c r="O40" s="6"/>
+      <c r="O40" s="7"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
@@ -4353,7 +5016,7 @@
       <c r="E41" s="4">
         <v>50</v>
       </c>
-      <c r="F41" s="6"/>
+      <c r="F41" s="7"/>
       <c r="G41" s="3" t="s">
         <v>294</v>
       </c>
@@ -4376,7 +5039,7 @@
       <c r="N41" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="O41" s="6"/>
+      <c r="O41" s="7"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
@@ -4411,7 +5074,7 @@
       <c r="E42" s="4">
         <v>50</v>
       </c>
-      <c r="F42" s="6"/>
+      <c r="F42" s="7"/>
       <c r="G42" s="3" t="s">
         <v>306</v>
       </c>
@@ -4432,7 +5095,7 @@
         <v>311</v>
       </c>
       <c r="N42" s="3"/>
-      <c r="O42" s="6"/>
+      <c r="O42" s="7"/>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
@@ -4484,7 +5147,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
-      <c r="O43" s="6"/>
+      <c r="O43" s="7"/>
       <c r="P43" s="3"/>
       <c r="Q43" s="3" t="s">
         <v>320</v>
@@ -4540,7 +5203,7 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
-      <c r="O44" s="6"/>
+      <c r="O44" s="7"/>
       <c r="P44" s="3"/>
       <c r="Q44" s="3" t="s">
         <v>327</v>
@@ -4596,7 +5259,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
-      <c r="O45" s="6"/>
+      <c r="O45" s="7"/>
       <c r="P45" s="3"/>
       <c r="Q45" s="3" t="s">
         <v>329</v>
@@ -4632,8 +5295,8 @@
       <c r="D46" s="4">
         <v>25</v>
       </c>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
       <c r="G46" s="3" t="s">
         <v>331</v>
       </c>
@@ -4648,7 +5311,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
-      <c r="O46" s="6"/>
+      <c r="O46" s="7"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
         <v>334</v>
@@ -4700,7 +5363,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
-      <c r="O47" s="6"/>
+      <c r="O47" s="7"/>
       <c r="P47" s="3"/>
       <c r="Q47" s="3" t="s">
         <v>341</v>
@@ -4756,7 +5419,7 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
-      <c r="O48" s="6"/>
+      <c r="O48" s="7"/>
       <c r="P48" s="3"/>
       <c r="Q48" s="3" t="s">
         <v>351</v>
@@ -4814,7 +5477,7 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
-      <c r="O49" s="6"/>
+      <c r="O49" s="7"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3" t="s">
         <v>329</v>
@@ -4853,7 +5516,7 @@
       <c r="E50" s="5">
         <v>40.1</v>
       </c>
-      <c r="F50" s="6"/>
+      <c r="F50" s="7"/>
       <c r="G50" s="3" t="s">
         <v>366</v>
       </c>
@@ -4868,7 +5531,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
-      <c r="O50" s="6"/>
+      <c r="O50" s="7"/>
       <c r="P50" s="3"/>
       <c r="Q50" s="3" t="s">
         <v>368</v>
@@ -4901,9 +5564,9 @@
       <c r="C51" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
       <c r="G51" s="3" t="s">
         <v>375</v>
       </c>
@@ -4924,7 +5587,7 @@
       <c r="N51" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="O51" s="6"/>
+      <c r="O51" s="7"/>
       <c r="P51" s="3"/>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
@@ -4955,9 +5618,9 @@
       <c r="C52" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
       <c r="G52" s="3" t="s">
         <v>384</v>
       </c>
@@ -4978,7 +5641,7 @@
       <c r="N52" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="O52" s="6"/>
+      <c r="O52" s="7"/>
       <c r="P52" s="3"/>
       <c r="Q52" s="3"/>
       <c r="R52" s="3" t="s">
@@ -5036,7 +5699,7 @@
       <c r="N53" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="7"/>
       <c r="P53" s="3"/>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5069,7 +5732,7 @@
       <c r="E54" s="4">
         <v>50</v>
       </c>
-      <c r="F54" s="6"/>
+      <c r="F54" s="7"/>
       <c r="G54" s="3" t="s">
         <v>404</v>
       </c>
@@ -5080,7 +5743,7 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
-      <c r="O54" s="6"/>
+      <c r="O54" s="7"/>
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -5115,7 +5778,7 @@
       <c r="E55" s="4">
         <v>50</v>
       </c>
-      <c r="F55" s="6"/>
+      <c r="F55" s="7"/>
       <c r="G55" s="3" t="s">
         <v>409</v>
       </c>
@@ -5126,7 +5789,7 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-      <c r="O55" s="6"/>
+      <c r="O55" s="7"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -5159,7 +5822,7 @@
       <c r="E56" s="5">
         <v>47.9</v>
       </c>
-      <c r="F56" s="6"/>
+      <c r="F56" s="7"/>
       <c r="G56" s="3" t="s">
         <v>414</v>
       </c>
@@ -5170,7 +5833,7 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-      <c r="O56" s="6"/>
+      <c r="O56" s="7"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
@@ -5207,7 +5870,7 @@
       <c r="E57" s="4">
         <v>50</v>
       </c>
-      <c r="F57" s="6"/>
+      <c r="F57" s="7"/>
       <c r="G57" s="3" t="s">
         <v>421</v>
       </c>
@@ -5218,7 +5881,7 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
-      <c r="O57" s="6"/>
+      <c r="O57" s="7"/>
       <c r="P57" s="3"/>
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
@@ -5245,9 +5908,9 @@
       <c r="C58" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
       <c r="G58" s="3" t="s">
         <v>425</v>
       </c>
@@ -5258,7 +5921,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="7"/>
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3" t="s">
@@ -5357,9 +6020,9 @@
       <c r="C60" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
       <c r="G60" s="3" t="s">
         <v>437</v>
       </c>
@@ -5370,7 +6033,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
-      <c r="O60" s="6"/>
+      <c r="O60" s="7"/>
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
@@ -5395,9 +6058,9 @@
       <c r="C61" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
       <c r="G61" s="3" t="s">
         <v>441</v>
       </c>
@@ -5408,7 +6071,7 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
-      <c r="O61" s="6"/>
+      <c r="O61" s="7"/>
       <c r="P61" s="3"/>
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
@@ -5440,8 +6103,8 @@
       <c r="D62" s="4">
         <v>25</v>
       </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
       <c r="G62" s="3" t="s">
         <v>446</v>
       </c>
@@ -5466,7 +6129,7 @@
       <c r="N62" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="O62" s="6"/>
+      <c r="O62" s="7"/>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
@@ -5567,9 +6230,9 @@
       <c r="C64" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
       <c r="G64" s="3" t="s">
         <v>469</v>
       </c>
@@ -5580,7 +6243,7 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
-      <c r="O64" s="6"/>
+      <c r="O64" s="7"/>
       <c r="P64" s="3"/>
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
@@ -5609,9 +6272,9 @@
       <c r="C65" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
       <c r="G65" s="3" t="s">
         <v>475</v>
       </c>
@@ -5626,7 +6289,7 @@
         <v>159</v>
       </c>
       <c r="N65" s="3"/>
-      <c r="O65" s="6"/>
+      <c r="O65" s="7"/>
       <c r="P65" s="3"/>
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
@@ -5651,9 +6314,9 @@
       <c r="C66" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
       <c r="G66" s="3" t="s">
         <v>480</v>
       </c>
@@ -5672,7 +6335,7 @@
         <v>484</v>
       </c>
       <c r="N66" s="3"/>
-      <c r="O66" s="6"/>
+      <c r="O66" s="7"/>
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
@@ -5697,9 +6360,9 @@
       <c r="C67" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
       <c r="G67" s="3" t="s">
         <v>488</v>
       </c>
@@ -5710,7 +6373,7 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-      <c r="O67" s="6"/>
+      <c r="O67" s="7"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3" t="s">
@@ -5727,7 +6390,7 @@
       </c>
       <c r="X67" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="20.25">
       <c r="A68" s="3" t="s">
         <v>491</v>
       </c>
@@ -5737,9 +6400,9 @@
       <c r="C68" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
       <c r="G68" s="3" t="s">
         <v>492</v>
       </c>
@@ -5750,7 +6413,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
-      <c r="O68" s="6"/>
+      <c r="O68" s="7"/>
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
@@ -5765,7 +6428,7 @@
       </c>
       <c r="X68" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="20.25">
       <c r="A69" s="3" t="s">
         <v>495</v>
       </c>
@@ -5775,9 +6438,9 @@
       <c r="C69" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
       <c r="G69" s="3" t="s">
         <v>496</v>
       </c>
@@ -5792,7 +6455,7 @@
         <v>49</v>
       </c>
       <c r="N69" s="3"/>
-      <c r="O69" s="6"/>
+      <c r="O69" s="7"/>
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
@@ -5807,7 +6470,7 @@
       </c>
       <c r="X69" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="20.25">
       <c r="A70" s="3" t="s">
         <v>500</v>
       </c>
@@ -5817,9 +6480,9 @@
       <c r="C70" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
       <c r="G70" s="3" t="s">
         <v>501</v>
       </c>
@@ -5832,7 +6495,7 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
-      <c r="O70" s="6"/>
+      <c r="O70" s="7"/>
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
@@ -5847,7 +6510,7 @@
       </c>
       <c r="X70" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="20.25">
       <c r="A71" s="3" t="s">
         <v>505</v>
       </c>
@@ -5857,9 +6520,9 @@
       <c r="C71" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
       <c r="G71" s="3" t="s">
         <v>506</v>
       </c>
@@ -5870,7 +6533,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
-      <c r="O71" s="6"/>
+      <c r="O71" s="7"/>
       <c r="P71" s="3"/>
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
@@ -5885,7 +6548,7 @@
       </c>
       <c r="X71" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="20.25">
       <c r="A72" s="3" t="s">
         <v>509</v>
       </c>
@@ -5895,9 +6558,9 @@
       <c r="C72" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
       <c r="G72" s="3" t="s">
         <v>510</v>
       </c>
@@ -5910,7 +6573,7 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
-      <c r="O72" s="6"/>
+      <c r="O72" s="7"/>
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
@@ -5925,7 +6588,7 @@
       </c>
       <c r="X72" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="20.25">
       <c r="A73" s="3" t="s">
         <v>514</v>
       </c>
@@ -5935,9 +6598,9 @@
       <c r="C73" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
       <c r="G73" s="3" t="s">
         <v>515</v>
       </c>
@@ -5948,7 +6611,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
-      <c r="O73" s="6"/>
+      <c r="O73" s="7"/>
       <c r="P73" s="3"/>
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
@@ -5963,7 +6626,7 @@
       </c>
       <c r="X73" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="20.25">
       <c r="A74" s="3" t="s">
         <v>518</v>
       </c>
@@ -5973,9 +6636,9 @@
       <c r="C74" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
       <c r="G74" s="3" t="s">
         <v>519</v>
       </c>
@@ -5986,7 +6649,7 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
-      <c r="O74" s="6"/>
+      <c r="O74" s="7"/>
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
@@ -6001,7 +6664,7 @@
       </c>
       <c r="X74" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="20.25">
       <c r="A75" s="3" t="s">
         <v>522</v>
       </c>
@@ -6011,9 +6674,9 @@
       <c r="C75" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
       <c r="G75" s="3" t="s">
         <v>523</v>
       </c>
@@ -6024,7 +6687,7 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
-      <c r="O75" s="6"/>
+      <c r="O75" s="7"/>
       <c r="P75" s="3"/>
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
@@ -6039,7 +6702,7 @@
       </c>
       <c r="X75" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="20.25">
       <c r="A76" s="3" t="s">
         <v>526</v>
       </c>
@@ -6049,9 +6712,9 @@
       <c r="C76" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
       <c r="G76" s="3" t="s">
         <v>527</v>
       </c>
@@ -6068,7 +6731,7 @@
         <v>529</v>
       </c>
       <c r="N76" s="3"/>
-      <c r="O76" s="6"/>
+      <c r="O76" s="7"/>
       <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
@@ -6085,7 +6748,7 @@
       </c>
       <c r="X76" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="20.25">
       <c r="A77" s="3" t="s">
         <v>532</v>
       </c>
@@ -6149,7 +6812,7 @@
       </c>
       <c r="X77" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="20.25">
       <c r="A78" s="3" t="s">
         <v>538</v>
       </c>
@@ -6159,9 +6822,9 @@
       <c r="C78" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
       <c r="G78" s="3" t="s">
         <v>539</v>
       </c>
@@ -6172,7 +6835,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
-      <c r="O78" s="6"/>
+      <c r="O78" s="7"/>
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
@@ -6191,7 +6854,7 @@
       </c>
       <c r="X78" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="20.25">
       <c r="A79" s="3" t="s">
         <v>543</v>
       </c>
@@ -6201,8 +6864,8 @@
       <c r="C79" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
       <c r="F79" s="4">
         <v>246000</v>
       </c>
@@ -6220,7 +6883,7 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
-      <c r="O79" s="6"/>
+      <c r="O79" s="7"/>
       <c r="P79" s="3"/>
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
@@ -6239,7 +6902,7 @@
       </c>
       <c r="X79" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="20.25">
       <c r="A80" s="3" t="s">
         <v>548</v>
       </c>
@@ -6249,9 +6912,9 @@
       <c r="C80" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
       <c r="G80" s="3" t="s">
         <v>198</v>
       </c>
@@ -6264,7 +6927,7 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
-      <c r="O80" s="6"/>
+      <c r="O80" s="7"/>
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
@@ -6281,7 +6944,7 @@
       </c>
       <c r="X80" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="20.25">
       <c r="A81" s="3" t="s">
         <v>552</v>
       </c>
@@ -6291,9 +6954,9 @@
       <c r="C81" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
       <c r="G81" s="3" t="s">
         <v>553</v>
       </c>
@@ -6304,7 +6967,7 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
-      <c r="O81" s="6"/>
+      <c r="O81" s="7"/>
       <c r="P81" s="3"/>
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
@@ -6331,9 +6994,9 @@
       <c r="C82" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
       <c r="G82" s="3" t="s">
         <v>557</v>
       </c>
@@ -6346,7 +7009,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-      <c r="O82" s="6"/>
+      <c r="O82" s="7"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
@@ -6373,9 +7036,9 @@
       <c r="C83" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
       <c r="G83" s="3" t="s">
         <v>562</v>
       </c>
@@ -6386,7 +7049,7 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
-      <c r="O83" s="6"/>
+      <c r="O83" s="7"/>
       <c r="P83" s="3"/>
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
@@ -6405,6 +7068,1694 @@
       </c>
       <c r="X83" s="3"/>
     </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+      <c r="A84" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="8"/>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="T84" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="W84" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="X84" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+      <c r="A85" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" s="8">
+        <v>10</v>
+      </c>
+      <c r="E85" s="8">
+        <v>41</v>
+      </c>
+      <c r="F85" s="8">
+        <v>161000</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="N85" s="3"/>
+      <c r="O85" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="P85" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q85" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="R85" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="S85" s="3"/>
+      <c r="T85" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="U85" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="V85" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="W85" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="X85" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+      <c r="A86" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="8"/>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3"/>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="W86" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="X86" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+      <c r="A87" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D87" s="8">
+        <v>24.6</v>
+      </c>
+      <c r="E87" s="8">
+        <v>47.9</v>
+      </c>
+      <c r="F87" s="8"/>
+      <c r="G87" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="N87" s="3"/>
+      <c r="O87" s="8"/>
+      <c r="P87" s="3"/>
+      <c r="Q87" s="3"/>
+      <c r="R87" s="3"/>
+      <c r="S87" s="3"/>
+      <c r="T87" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="U87" s="3"/>
+      <c r="V87" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="W87" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="X87" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+      <c r="A88" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="8"/>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3"/>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="W88" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="X88" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+      <c r="A89" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" s="8">
+        <v>25</v>
+      </c>
+      <c r="E89" s="8">
+        <v>57</v>
+      </c>
+      <c r="F89" s="8"/>
+      <c r="G89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="N89" s="3"/>
+      <c r="O89" s="8">
+        <v>8</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="X89" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+      <c r="A90" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="8"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="W90" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="X90" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+      <c r="A91" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="N91" s="3"/>
+      <c r="O91" s="8"/>
+      <c r="P91" s="3"/>
+      <c r="Q91" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="S91" s="3"/>
+      <c r="T91" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="X91" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+      <c r="A92" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="8"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3"/>
+      <c r="S92" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="T92" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="W92" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="X92" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+      <c r="A93" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="N93" s="3"/>
+      <c r="O93" s="8"/>
+      <c r="P93" s="3"/>
+      <c r="Q93" s="3"/>
+      <c r="R93" s="3"/>
+      <c r="S93" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="T93" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="U93" s="3"/>
+      <c r="V93" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="W93" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="X93" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="N94" s="3"/>
+      <c r="O94" s="8"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+      <c r="S94" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="X94" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+      <c r="A95" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="8"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="T95" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="W95" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="X95" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+      <c r="A96" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="F96" s="8">
+        <v>100000</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="O96" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="T96" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="W96" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="X96" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+      <c r="A97" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="8"/>
+      <c r="P97" s="3"/>
+      <c r="Q97" s="3"/>
+      <c r="R97" s="3"/>
+      <c r="S97" s="3"/>
+      <c r="T97" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="U97" s="3"/>
+      <c r="V97" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="W97" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="X97" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+      <c r="A98" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="8"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3"/>
+      <c r="S98" s="3"/>
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="W98" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="X98" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+      <c r="A99" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="8"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
+      <c r="R99" s="3"/>
+      <c r="S99" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="T99" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="U99" s="3"/>
+      <c r="V99" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="W99" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="X99" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+      <c r="A100" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" s="8">
+        <v>25</v>
+      </c>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="N100" s="3"/>
+      <c r="O100" s="8">
+        <v>10.09</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="S100" s="3"/>
+      <c r="T100" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="X100" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+      <c r="A101" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="8"/>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3"/>
+      <c r="R101" s="3"/>
+      <c r="S101" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="U101" s="3"/>
+      <c r="V101" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="X101" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+      <c r="A102" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="N102" s="3"/>
+      <c r="O102" s="8"/>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
+      <c r="S102" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="U102" s="3"/>
+      <c r="V102" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="X102" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+      <c r="A103" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="8"/>
+      <c r="P103" s="3"/>
+      <c r="Q103" s="3"/>
+      <c r="R103" s="3"/>
+      <c r="S103" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="T103" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="U103" s="3"/>
+      <c r="V103" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="W103" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="X103" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+      <c r="A104" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="8"/>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3"/>
+      <c r="S104" s="3"/>
+      <c r="T104" s="3"/>
+      <c r="U104" s="3"/>
+      <c r="V104" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="W104" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="X104" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+      <c r="A105" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N105" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O105" s="8"/>
+      <c r="P105" s="3"/>
+      <c r="Q105" s="3"/>
+      <c r="R105" s="3"/>
+      <c r="S105" s="3"/>
+      <c r="T105" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="U105" s="3"/>
+      <c r="V105" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="W105" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="X105" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+      <c r="A106" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="8"/>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+      <c r="R106" s="3"/>
+      <c r="S106" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="T106" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="U106" s="3"/>
+      <c r="V106" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="W106" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="X106" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+      <c r="A107" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D107" s="8">
+        <v>25</v>
+      </c>
+      <c r="E107" s="8">
+        <v>57</v>
+      </c>
+      <c r="F107" s="8"/>
+      <c r="G107" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K107" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="M107" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="N107" s="3"/>
+      <c r="O107" s="8">
+        <v>12</v>
+      </c>
+      <c r="P107" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q107" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="R107" s="3"/>
+      <c r="S107" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="T107" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="U107" s="3"/>
+      <c r="V107" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="W107" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="X107" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+      <c r="A108" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+      <c r="O108" s="8"/>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3"/>
+      <c r="S108" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="T108" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="U108" s="3"/>
+      <c r="V108" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="W108" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="X108" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+      <c r="A109" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="8"/>
+      <c r="P109" s="3"/>
+      <c r="Q109" s="3"/>
+      <c r="R109" s="3"/>
+      <c r="S109" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="T109" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="U109" s="3"/>
+      <c r="V109" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="W109" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="X109" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
+      <c r="A110" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110" s="8">
+        <v>25</v>
+      </c>
+      <c r="E110" s="8">
+        <v>57</v>
+      </c>
+      <c r="F110" s="8"/>
+      <c r="G110" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="N110" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="O110" s="8">
+        <v>12</v>
+      </c>
+      <c r="P110" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="Q110" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="R110" s="3"/>
+      <c r="S110" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="T110" s="3"/>
+      <c r="U110" s="3"/>
+      <c r="V110" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="W110" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="X110" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+      <c r="A111" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
+      <c r="O111" s="8"/>
+      <c r="P111" s="3"/>
+      <c r="Q111" s="3"/>
+      <c r="R111" s="3"/>
+      <c r="S111" s="3"/>
+      <c r="T111" s="3"/>
+      <c r="U111" s="3"/>
+      <c r="V111" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="W111" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="X111" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
+      <c r="A112" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M112" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="N112" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="O112" s="8">
+        <v>10</v>
+      </c>
+      <c r="P112" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q112" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="R112" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="S112" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="T112" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="U112" s="3"/>
+      <c r="V112" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="W112" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="X112" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+      <c r="A113" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3"/>
+      <c r="O113" s="8"/>
+      <c r="P113" s="3"/>
+      <c r="Q113" s="3"/>
+      <c r="R113" s="3"/>
+      <c r="S113" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="T113" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="U113" s="3"/>
+      <c r="V113" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="W113" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="X113" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+      <c r="A114" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D114" s="8"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
+      <c r="O114" s="8"/>
+      <c r="P114" s="3"/>
+      <c r="Q114" s="3"/>
+      <c r="R114" s="3"/>
+      <c r="S114" s="3"/>
+      <c r="T114" s="3"/>
+      <c r="U114" s="3"/>
+      <c r="V114" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="W114" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="X114" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+      <c r="A115" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D115" s="8">
+        <v>19</v>
+      </c>
+      <c r="E115" s="8">
+        <v>10</v>
+      </c>
+      <c r="F115" s="8"/>
+      <c r="G115" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="N115" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="O115" s="8"/>
+      <c r="P115" s="3"/>
+      <c r="Q115" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="R115" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="S115" s="3"/>
+      <c r="T115" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="U115" s="3"/>
+      <c r="V115" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="W115" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="X115" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+      <c r="A116" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D116" s="8">
+        <v>25</v>
+      </c>
+      <c r="E116" s="8">
+        <v>57</v>
+      </c>
+      <c r="F116" s="8"/>
+      <c r="G116" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="M116" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="N116" s="3"/>
+      <c r="O116" s="8">
+        <v>13.8</v>
+      </c>
+      <c r="P116" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q116" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="R116" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="S116" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="T116" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="U116" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="V116" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="W116" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="X116" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
+      <c r="A117" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D117" s="8">
+        <v>25</v>
+      </c>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K117" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L117" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="M117" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="N117" s="3"/>
+      <c r="O117" s="8"/>
+      <c r="P117" s="3"/>
+      <c r="Q117" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="R117" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="S117" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="T117" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="U117" s="3"/>
+      <c r="V117" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="W117" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="X117" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dataset/数据.xlsx
+++ b/dataset/数据.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="672">
   <si>
     <t>样本ID</t>
   </si>
@@ -256,1147 +256,1126 @@
     <t>10.1021/acs.iecr.6b02259</t>
   </si>
   <si>
-    <t>SSBR-016</t>
+    <t>SSBR-017</t>
+  </si>
+  <si>
+    <t>硅橡胶/SSBR界面改性</t>
+  </si>
+  <si>
+    <t>TMPMP</t>
+  </si>
+  <si>
+    <t>OCC(C)(COC(=O)CCS)COC(=O)CCS</t>
+  </si>
+  <si>
+    <t>C(=O)OCC</t>
+  </si>
+  <si>
+    <t>酯基</t>
+  </si>
+  <si>
+    <t>-COOR</t>
+  </si>
+  <si>
+    <t>OCC(C)(COC(=O)CCS)COC(=O)CCS---23.5---S-C(=O)OCC--</t>
+  </si>
+  <si>
+    <t>文献 Fig.5</t>
+  </si>
+  <si>
+    <t>文献 Fig.6</t>
+  </si>
+  <si>
+    <t>Sun Z, et al. [J]. Ind. Eng. Chem. Res. 2017, 56(6): 1471-1477.</t>
+  </si>
+  <si>
+    <t>10.1021/acs.iecr.6b04146</t>
+  </si>
+  <si>
+    <t>SSBR-018</t>
+  </si>
+  <si>
+    <t>二氧化硅分散</t>
+  </si>
+  <si>
+    <t>DPE-NMe2</t>
+  </si>
+  <si>
+    <t>CN(C)c1ccc(C(=C)c2ccccc2)cc1</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>氨基</t>
+  </si>
+  <si>
+    <t>-NMe2</t>
+  </si>
+  <si>
+    <t>CN(C)c1ccc(C(=C)c2ccccc2)cc1---------N--</t>
+  </si>
+  <si>
+    <t>文献 Fig.1</t>
+  </si>
+  <si>
+    <t>Sun C, et al. [J]. Ind. Eng. Chem. Res. 2019, 58.</t>
+  </si>
+  <si>
+    <t>10.1021/acs.iecr.8b05738</t>
+  </si>
+  <si>
+    <t>SSBR-021</t>
+  </si>
+  <si>
+    <t>Sun C, Shipeng W, Ma H, et al. Improvement of silica dispersion in solution polymerized styrene-butadiene rubber via introducing amino functional groups[J]. Industrial &amp; Engineering Chemistry Research, 2019, 58(2): 586-592.</t>
+  </si>
+  <si>
+    <t>SSBR-022</t>
+  </si>
+  <si>
+    <t>石墨烯/橡胶复合材料</t>
+  </si>
+  <si>
+    <t>TPES</t>
+  </si>
+  <si>
+    <t>C=Cc1ccc(CC(c2ccccc2)(c3ccccc3)c4ccccc4)cc1</t>
+  </si>
+  <si>
+    <t>c1ccc(C(c2ccccc2)(c3ccccc3)c4ccccc4)cc1</t>
+  </si>
+  <si>
+    <t>三苯基乙基</t>
+  </si>
+  <si>
+    <t>-CPh3</t>
+  </si>
+  <si>
+    <t>C=Cc1ccc(CC(c2ccccc2)(c3ccccc3)c4ccccc4)cc1-168000-24.0-----c1ccc(C(c2ccccc2)(c3ccccc3)c4ccccc4)cc1-0.9wt%</t>
+  </si>
+  <si>
+    <t>Huang M, Lu J, Han B, et al. Covalent approach for in situ enhancement of interaction between pristine graphene and styrene-butadiene-p-(2,2,2-triphenylethyl)styrene rubber[J]. Journal of Applied Polymer Science, 2017, 134(28): 44923.</t>
+  </si>
+  <si>
+    <t>10.1002/app.44923</t>
+  </si>
+  <si>
+    <t>SSBR-023</t>
+  </si>
+  <si>
+    <t>二氧化硅填料分散</t>
+  </si>
+  <si>
+    <t>3-巯基丙酸(3-MPA)</t>
+  </si>
+  <si>
+    <t>SCCC(=O)O</t>
+  </si>
+  <si>
+    <t>mol %</t>
+  </si>
+  <si>
+    <t>SCCC(=O)O-223900-23.4-47.3-S-C(=O)O-1.7mol %</t>
+  </si>
+  <si>
+    <t>文献 Fig.10</t>
+  </si>
+  <si>
+    <t>文献 Fig.12</t>
+  </si>
+  <si>
+    <t>Wang L, Lu Y, Xie X, et al. In situ grafting onto solution polymerized styrene butadiene rubbers (SSBR) filled with silica via solid state method[J]. Journal of Applied Polymer Science, 2018, 135(34): 46653.</t>
+  </si>
+  <si>
+    <t>10.1002/app.46653</t>
+  </si>
+  <si>
+    <t>SSBR-024</t>
+  </si>
+  <si>
+    <t>MMP</t>
+  </si>
+  <si>
+    <t>Cn1cc[nH+]c1.SCCC(=O)[O-]</t>
+  </si>
+  <si>
+    <t>C[n+]1ccn(C)c1</t>
+  </si>
+  <si>
+    <t>咪唑鎓</t>
+  </si>
+  <si>
+    <t>-Im+</t>
+  </si>
+  <si>
+    <t>Cn1cc[nH+]c1.SCCC(=O)[O-]---27.0---S-C[n+]1ccn(C)c1-14.8mol %</t>
+  </si>
+  <si>
+    <t>文献 Fig.7</t>
+  </si>
+  <si>
+    <t>Weng P, Tang Z, Huang J, et al. Promoted dispersion of silica and interfacial strength in rubber/silica composites by grafting with oniums[J]. Journal of Applied Polymer Science, 2019, 136(44): 48243.</t>
+  </si>
+  <si>
+    <t>10.1002/app.48243</t>
+  </si>
+  <si>
+    <t>SSBR-025</t>
+  </si>
+  <si>
+    <t>轮胎胎面胶</t>
+  </si>
+  <si>
+    <t>丙胺, 二甲氧基硅烷</t>
+  </si>
+  <si>
+    <t>NCC.CO[SiH](OC)C</t>
+  </si>
+  <si>
+    <t>N.[Si](O)(O)O</t>
+  </si>
+  <si>
+    <t>氨基/硅烷基</t>
+  </si>
+  <si>
+    <t>-NH2/-Si(OR)3</t>
+  </si>
+  <si>
+    <t>NCC.CO[SiH](OC)C---36.0-26.0---N.[Si](O)(O)O--</t>
+  </si>
+  <si>
+    <t>文献 Table III</t>
+  </si>
+  <si>
+    <t>Sirisinha C, Sae-oui P, Suchiva K, et al. Properties of tire tread compounds based on functionalized styrene butadiene rubber and functionalized natural rubber[J]. Journal of Applied Polymer Science, 2019, 137(13): 48696.</t>
+  </si>
+  <si>
+    <t>10.1002/app.48696</t>
+  </si>
+  <si>
+    <t>SSBR-026</t>
   </si>
   <si>
     <t>炭黑分散改性</t>
   </si>
   <si>
-    <t>DPES</t>
+    <t>β-月桂烯</t>
+  </si>
+  <si>
+    <t>CC(C)=CCCC(=C)C=C</t>
+  </si>
+  <si>
+    <t>CC(C)</t>
+  </si>
+  <si>
+    <t>异亚丙基侧链</t>
+  </si>
+  <si>
+    <t>-C(CH3)2-</t>
+  </si>
+  <si>
+    <t>CC(C)=CCCC(=C)C=C-150000-------CC(C)--</t>
+  </si>
+  <si>
+    <t>Zhang J, Lu J, Su K, et al. Bio-based β-myrcene-modiﬁed solution-polymerized styrene-butadiene rubber for improving carbon black dispersion and wet skid resistance[J]. Journal of Applied Polymer Science, 2019, 136(30): 48159.</t>
+  </si>
+  <si>
+    <t>10.1002/app.48159</t>
+  </si>
+  <si>
+    <t>SSBR-030</t>
+  </si>
+  <si>
+    <t>3-巯基丙酸 (3-MPA)</t>
+  </si>
+  <si>
+    <t>SCCC(=O)O-206600-21.0---S-C(=O)O-2.4wt%</t>
+  </si>
+  <si>
+    <t>文献 Fig.8 TEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.2 Payne效应</t>
+  </si>
+  <si>
+    <t>文献 Fig.11 DSC曲线</t>
+  </si>
+  <si>
+    <t>Qu L, Zhang W, Yang H, et al. Contribution of silica interaction with functionalized SSBR on the performance of green tire tread compounds[J]. RSC Advances, 2014, 4(109): 64354-64362.</t>
+  </si>
+  <si>
+    <t>10.1039/c4ra09492a</t>
+  </si>
+  <si>
+    <t>SSBR-031</t>
+  </si>
+  <si>
+    <t>绿色轮胎、高分散白炭黑复合材料</t>
+  </si>
+  <si>
+    <t>SCCC(=O)O-214700-20.7---S-C(=O)O-2.4wt%</t>
+  </si>
+  <si>
+    <t>文献 Fig.7 TEM图</t>
+  </si>
+  <si>
+    <t>Luo Y, Qu L, Su H, et al. Effect of chemical structure of elastomer on filler dispersion and interactions in silica/solution-polymerized styrene butadiene rubber composites through molecular dynamics simulation[J]. RSC Advances, 2016, 6(17): 14643-14650.</t>
+  </si>
+  <si>
+    <t>10.1039/c5ra24965a</t>
+  </si>
+  <si>
+    <t>SSBR-033</t>
+  </si>
+  <si>
+    <t>高性能轮胎、节能环保轮胎</t>
+  </si>
+  <si>
+    <t>1,5-萘二异氰酸酯 (NDI)</t>
+  </si>
+  <si>
+    <t>O=C=Nc1ccc2c(N=C=O)ccc12</t>
+  </si>
+  <si>
+    <t>异氰酸根</t>
+  </si>
+  <si>
+    <t>N=C=O</t>
+  </si>
+  <si>
+    <t>NC(=O)O</t>
+  </si>
+  <si>
+    <t>聚氨酯硬段</t>
+  </si>
+  <si>
+    <t>-NHCOO-</t>
+  </si>
+  <si>
+    <t>O=C=Nc1ccc2c(N=C=O)ccc12-------N=C=O-NC(=O)O--</t>
   </si>
   <si>
     <t>文献 Fig.2</t>
   </si>
   <si>
+    <t>文献 Fig.7 SEM图</t>
+  </si>
+  <si>
+    <t>文献 Table 1</t>
+  </si>
+  <si>
+    <t>Qin X, Wang J, Han B, et al. Novel Design of Eco-Friendly Super Elastomer Materials With Optimized Hard Segments Micro-Structure: Toward Next-Generation High-Performance Tires[J]. Frontiers in Chemistry, 2018, 6: 240.</t>
+  </si>
+  <si>
+    <t>10.3389/fchem.2018.00240</t>
+  </si>
+  <si>
+    <t>SSBR-034</t>
+  </si>
+  <si>
+    <t>超疏水涂层、输送带</t>
+  </si>
+  <si>
+    <t>三羟甲基丙烷三(3-巯基丙酸)酯 (TMPMP)</t>
+  </si>
+  <si>
+    <t>CCC(COC(=O)CCS)(COC(=O)CCS)COC(=O)CCS</t>
+  </si>
+  <si>
+    <t>CCC(COC(=O)CCS)(COC(=O)CCS)COC(=O)CCS-160200-----S-C(=O)OCC-10wt%</t>
+  </si>
+  <si>
+    <t>文献 Fig.S1</t>
+  </si>
+  <si>
+    <t>文献 Fig.5 SEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.7 粘附力曲线</t>
+  </si>
+  <si>
+    <t>Ning N, Wang S, Zhang Z, et al. Superhydrophobic coating with Ultrahigh Adhesive Force and Good Anti-scratching on Elastomeric Substrate by Thiol-ene Click Chemistry[J]. Chemical Engineering Journal, 2019, 370: 1100-1108.</t>
+  </si>
+  <si>
+    <t>10.1016/j.cej.2019.04.215</t>
+  </si>
+  <si>
+    <t>SSBR-036</t>
+  </si>
+  <si>
+    <t>绿色轮胎</t>
+  </si>
+  <si>
+    <t>双环氧丙基多硫化物 (BEP)</t>
+  </si>
+  <si>
+    <t>C1OC1CSSSSCC2CO2</t>
+  </si>
+  <si>
+    <t>C1OC1</t>
+  </si>
+  <si>
+    <t>环氧基</t>
+  </si>
+  <si>
+    <t>-C2H2O-</t>
+  </si>
+  <si>
+    <t>C1OC1CSSSSCC2CO2---25.0-50.0---C1OC1--</t>
+  </si>
+  <si>
+    <t>文献 Fig.11 损耗因子</t>
+  </si>
+  <si>
+    <t>Ye N, Zheng J, Xin Y, et al. Performance enhancement of rubber composites using VOC-Free interfacial silica coupling agent[J]. Composites Part B: Engineering, 2020, 202: 108301.</t>
+  </si>
+  <si>
+    <t>10.1016/j.compositesb.2020.108301</t>
+  </si>
+  <si>
+    <t>SSBR-038</t>
+  </si>
+  <si>
+    <t>气体阻隔材料、复合材料</t>
+  </si>
+  <si>
+    <t>1-庚硫醇、1-十八烷硫醇</t>
+  </si>
+  <si>
+    <t>CCCCCCC S</t>
+  </si>
+  <si>
+    <t>CCCCCC</t>
+  </si>
+  <si>
+    <t>烷基链</t>
+  </si>
+  <si>
+    <t>-(CH2)n-</t>
+  </si>
+  <si>
+    <t>CCCCCCC S---25.0-50.0-S-CCCCCC--</t>
+  </si>
+  <si>
+    <t>文献 Fig.7 存储模量</t>
+  </si>
+  <si>
+    <t>Luo Y, Wu Y, Luo K, et al. Structures and properties of alkanethiol-modified graphene oxide/solution-polymerized styrene butadiene rubber composites: Click chemistry and molecular dynamics simulation[J]. Composites Science and Technology, 2018, 161: 32-38.</t>
+  </si>
+  <si>
+    <t>10.1016/j.compscitech.2018.03.036</t>
+  </si>
+  <si>
+    <t>SSBR-040</t>
+  </si>
+  <si>
+    <t>轮胎、高耐磨复合材料</t>
+  </si>
+  <si>
+    <t>六甲基二硅氮烷 (HMDS)</t>
+  </si>
+  <si>
+    <t>CC[Si](C)(C)N[Si](C)(C)C</t>
+  </si>
+  <si>
+    <t>硅氮基</t>
+  </si>
+  <si>
+    <t>[Si]N</t>
+  </si>
+  <si>
+    <t>[Si](C)(C)C</t>
+  </si>
+  <si>
+    <t>三甲基硅基</t>
+  </si>
+  <si>
+    <t>-Si(CH3)3</t>
+  </si>
+  <si>
+    <t>CC[Si](C)(C)N[Si](C)(C)C---25.0-50.0-[Si]N-[Si](C)(C)C--</t>
+  </si>
+  <si>
+    <t>文献 Fig.11 SEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.8 拉伸强度</t>
+  </si>
+  <si>
+    <t>Tian Q, Zhang C, Tang Y, et al. Preparation of hexamethyl disilazane-surface functionalized nano-silica by controlling surface chemistry and its “agglomeration-collapse” behavior in solution polymerized styrene butadiene rubber/butadiene rubber composites[J]. Composites Science and Technology, 2021, 201: 108482.</t>
+  </si>
+  <si>
+    <t>10.1016/j.compscitech.2020.108482</t>
+  </si>
+  <si>
+    <t>SSBR-041</t>
+  </si>
+  <si>
+    <t>高性能抗老化轮胎</t>
+  </si>
+  <si>
+    <t>N-(4-苯胺基苯基)马来酰亚胺 (MC)</t>
+  </si>
+  <si>
+    <t>O=C1C=CC(=O)N1c2ccc(Nc3ccccc3)cc2</t>
+  </si>
+  <si>
+    <t>马来酰亚胺基</t>
+  </si>
+  <si>
+    <t>N1C(=O)C=CC1=O</t>
+  </si>
+  <si>
+    <t>Nc1ccc(N)cc1</t>
+  </si>
+  <si>
+    <t>对苯二胺衍生物</t>
+  </si>
+  <si>
+    <t>-C6H4(NH2)2</t>
+  </si>
+  <si>
+    <t>O=C1C=CC(=O)N1c2ccc(Nc3ccccc3)cc2---25.0-50.0-N1C(=O)C=CC1=O-Nc1ccc(N)cc1--</t>
+  </si>
+  <si>
+    <t>文献 Fig.10 TEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.7 拉伸曲线</t>
+  </si>
+  <si>
+    <t>Luo K, Zheng W, Zhao X, et al. Effects of antioxidant functionalized silica on reinforcement and anti-aging for solution-polymerized styrene butadiene rubber: Experimental and molecular simulation study[J]. Materials &amp; Design, 2018, 154: 114-125.</t>
+  </si>
+  <si>
+    <t>10.1016/j.matdes.2018.05.048</t>
+  </si>
+  <si>
+    <t>SSBR-042</t>
+  </si>
+  <si>
+    <t>绿色轮胎胎面材料</t>
+  </si>
+  <si>
+    <t>[3-(2-氨基乙基)氨基丙基]三甲氧基硅烷（AMMO）</t>
+  </si>
+  <si>
+    <t>COC[Si](CCC(NCCN)OC)(OC)OC</t>
+  </si>
+  <si>
+    <t>N.[Si](OC)(OC)OC</t>
+  </si>
+  <si>
+    <t>氨基/三甲氧基硅烷基</t>
+  </si>
+  <si>
+    <t>-NH2/-Si(OCH₃)₃</t>
+  </si>
+  <si>
+    <t>COC[Si](CCC(NCCN)OC)(OC)OC-258000-21.1-38.1---N.[Si](OC)(OC)OC--</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 共凝聚橡胶的TEM照片；文献 Fig.7 SSBR/SiO2和N-SSBR/SiO2纳米复合材料的TEM照片</t>
+  </si>
+  <si>
+    <t>文献 Fig.5 SSBR/SiO2和N-SSBR/SiO2纳米复合材料的G'-应变曲线；文献 Fig.6 SSBR/SiO2和N-SSBR/SiO2纳米复合材料的tanδ-应变曲线</t>
+  </si>
+  <si>
+    <t>文献 Fig.3 生胶和共凝聚橡胶的G'-T和tanδ-T曲线；文献 Fig.4 SSBR/SiO2和N-SSBR/SiO2纳米复合材料的G'-T和tanδ-T曲线</t>
+  </si>
+  <si>
+    <t>Liu X, Zhao S H. Study on Structure and Properties of SSBR/SiO2 Co-coagulated Rubber and SSBR Filled with Nanosilica Composites[J]. Journal of Applied Polymer Science, 2008, 109(6): 3900-3907.</t>
+  </si>
+  <si>
+    <t>10.1002/app.28621</t>
+  </si>
+  <si>
+    <t>SSBR-043</t>
+  </si>
+  <si>
+    <t>COC[Si](CCC(NCCN)OC)(OC)OC-336000-24.2-46.0---N.[Si](OC)(OC)OC--</t>
+  </si>
+  <si>
+    <t>SSBR-044</t>
+  </si>
+  <si>
+    <t>COC[Si](CCC(NCCN)OC)(OC)OC-351000-29.5-34.7---N.[Si](OC)(OC)OC--</t>
+  </si>
+  <si>
+    <t>SSBR-045</t>
+  </si>
+  <si>
+    <t>轮胎胎面</t>
+  </si>
+  <si>
+    <t>3-辛酰硫基-1-丙基三乙氧基硅烷</t>
+  </si>
+  <si>
+    <t>CCCCCCCC(=O)SCCC[Si](OCC)(OCC)OCC</t>
+  </si>
+  <si>
+    <t>CCCCCCCC(=O)SCCC[Si](OCC)(OCC)OCC---25.0-----[Si](OCC)(OCC)OCC--</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 不同填料含量的SiO2/SSBR复合材料在不同γ值下的G(t,γ)随时间t变化曲线；文献 Fig.3 不同填料含量的SiO2/SSBR复合材料的h(γ)随γ变化曲线</t>
+  </si>
+  <si>
+    <t>Sun J, Li H, Song Y H, et al. Nonlinear Stress Relaxation of Silica Filled Solution-Polymerized Styrene–Butadiene Rubber Compounds[J]. Journal of Applied Polymer Science, 2009, 112(6): 3569-3574.</t>
+  </si>
+  <si>
+    <t>10.1002/app.29646</t>
+  </si>
+  <si>
+    <t>SSBR-046</t>
+  </si>
+  <si>
+    <t>双[γ-(三乙氧基硅基)丙基]二硫化物（Si-75）</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC</t>
+  </si>
+  <si>
+    <t>[Si](OCC)(OCC)OCC.SS</t>
+  </si>
+  <si>
+    <t>三乙氧基硅烷基/二硫化物</t>
+  </si>
+  <si>
+    <t>-Si(OC₂H₅)₃/-S-S-</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC-123000-27.5-25.4---[Si](OCC)(OCC)OCC.SS--</t>
+  </si>
+  <si>
+    <t>文献 Fig.3 SSBR/SiO2/CB纳米复合材料的TEM照片</t>
+  </si>
+  <si>
+    <t>文献 Fig.4 SSBR/SiO2/CB纳米复合材料的G'-应变和tanδ-应变曲线</t>
+  </si>
+  <si>
+    <t>文献 Fig.4 SSBR/SiO2/CB纳米复合材料的tanδ-温度曲线</t>
+  </si>
+  <si>
+    <t>Wang L, Zhao S H. Study on the Structure-Mechanical Properties Relationship and Antistatic Characteristics of SSBR Composites Filled with SiO2/CB[J]. Journal of Applied Polymer Science, 2010, 118(1): 338-345.</t>
+  </si>
+  <si>
+    <t>10.1002/app.32372</t>
+  </si>
+  <si>
+    <t>SSBR-047</t>
+  </si>
+  <si>
+    <t>绿色轮胎胎面</t>
+  </si>
+  <si>
+    <t>双-(三乙氧基硅基丙基)-四硫化物（TESPT）、双-(三乙氧基硅基丙基)-二硫化物（TESPD）</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC</t>
+  </si>
+  <si>
+    <t>[Si](OCC)(OCC)OCC.SSSS</t>
+  </si>
+  <si>
+    <t>三乙氧基硅烷基/多硫化物</t>
+  </si>
+  <si>
+    <t>-Si(OC₂H₅)₃/-Sₓ-</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC-167000-24.8-9.7---[Si](OCC)(OCC)OCC.SSSS--</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 未改性二氧化硅和硅烷改性二氧化硅的FTIR谱图</t>
+  </si>
+  <si>
+    <t>文献 Fig.2 SSBR/二氧化硅纳米复合材料的TEM照片</t>
+  </si>
+  <si>
+    <t>文献 Fig.5 填充SSBR的储能模量-动态应变曲线；文献 Fig.7 填充SSBR的应力-应变曲线</t>
+  </si>
+  <si>
+    <t>文献 Fig.8 填充SSBR的储能模量-温度曲线、损耗因子-温度曲线</t>
+  </si>
+  <si>
+    <t>Qu L L, Yu G Z, Wang L L, et al. Effect of Filler–Elastomer Interactions on the Mechanical and Nonlinear Viscoelastic Behaviors of Chemically Modified Silica-Reinforced Solution-Polymerized Styrene Butadiene Rubber[J]. Journal of Applied Polymer Science, 2012, 125(2): 1174-1184.</t>
+  </si>
+  <si>
+    <t>10.1002/app.36677</t>
+  </si>
+  <si>
+    <t>SSBR-048</t>
+  </si>
+  <si>
+    <t>[3-(2-氨基乙基)氨基丙基]三甲氧基硅烷</t>
+  </si>
+  <si>
+    <t>文献 Fig.2 N-SSBR的¹H NMR谱图</t>
+  </si>
+  <si>
+    <t>文献 Fig.3 N-SSBR和SSBR/SiO2/CB纳米复合材料的TEM照片；文献 Fig.6 硫化胶弯曲断裂表面的SEM照片</t>
+  </si>
+  <si>
+    <t>文献 Fig.4 SSBR/SiO2/CB和N-SSBR/SiO2/CB纳米复合材料的G'-应变和tanδ-应变曲线</t>
+  </si>
+  <si>
+    <t>Liu X, Zhao S H, Yang Y, et al. Dynamic Properties of Star-Shaped, Solution-Polymerized Styrene–Butadiene Rubber and Its Cocoagulated Rubber-Filled with Silica/Carbon Black[J]. Journal of Applied Polymer Science, 2014, 131(11): 40348.</t>
+  </si>
+  <si>
+    <t>10.1002/app.40348</t>
+  </si>
+  <si>
+    <t>SSBR-049</t>
+  </si>
+  <si>
+    <t>乘用车轮胎胎面胶</t>
+  </si>
+  <si>
+    <t>双-(3-(三乙氧基硅基)-丙基)-四硫化物（TESPT，Si-69）</t>
+  </si>
+  <si>
+    <t>三乙氧基硅烷基/四硫化物</t>
+  </si>
+  <si>
+    <t>-Si(OC₂H₅)₃/-S₄-</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC---34.6-40.1---[Si](OCC)(OCC)OCC.SSSS--</t>
+  </si>
+  <si>
+    <t>文献 Fig.4 不同硅烷化温度下二氧化硅填充硫化胶的TEM照片</t>
+  </si>
+  <si>
+    <t>文献 Fig.7 0℃下硫化胶损耗因子随动态应变的变化曲线；文献 Fig.8 60℃下硫化胶损耗因子随动态应变的变化曲线</t>
+  </si>
+  <si>
+    <t>文献 Fig.6 不同硅烷化温度下硫化胶的损耗因子(tanδ)随测试温度的变化曲线</t>
+  </si>
+  <si>
+    <t>Thaptong P, Sae-Oui P, Sirisinha C. Effects of silanization temperature and silica type on properties of silica-filled solution styrene butadiene rubber (SSBR) for passenger car tire tread compounds[J]. Journal of Applied Polymer Science, 2016, 133(17): 43342.</t>
+  </si>
+  <si>
+    <t>10.1002/app.43342</t>
+  </si>
+  <si>
+    <t>SSBR-050</t>
+  </si>
+  <si>
+    <t>极低滚阻节能轮胎</t>
+  </si>
+  <si>
+    <t>环氧乙烷</t>
+  </si>
+  <si>
+    <t>C1CO1</t>
+  </si>
+  <si>
+    <t>[OH]</t>
+  </si>
+  <si>
+    <t>C1CO1---------[OH]--</t>
+  </si>
+  <si>
+    <t>文献 Fig.9 损耗因子</t>
+  </si>
+  <si>
+    <t>文献 Fig.15 DSC曲线</t>
+  </si>
+  <si>
+    <t>Qin X, Han B, Lu J, et al. Rational Design of Advanced Elastomer Nanocomposites Towards Extremely Energy-saving Tires Based on Macromolecular Assembly Strategy[J]. Nano Energy, 2018, 48: 180-188.</t>
+  </si>
+  <si>
+    <t>10.1016/j.nanoen.2018.03.038</t>
+  </si>
+  <si>
+    <t>SSBR-051</t>
+  </si>
+  <si>
+    <t>炭黑填充 SSBR 复合材料</t>
+  </si>
+  <si>
+    <t>叔丁基氯二苯基硅烷 (TBCSi)</t>
+  </si>
+  <si>
+    <t>CC(C)(C)[Si](Cl)(c1ccccc1)c2ccccc2</t>
+  </si>
+  <si>
+    <t>[Si]</t>
+  </si>
+  <si>
+    <t>硅基</t>
+  </si>
+  <si>
+    <t>-SiR3</t>
+  </si>
+  <si>
+    <t>CC(C)(C)[Si](Cl)(c1ccccc1)c2ccccc2---------[Si]--</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 ¹H NMR谱图</t>
+  </si>
+  <si>
+    <t>文献 Fig.5 损耗因子</t>
+  </si>
+  <si>
+    <t>文献 Fig.3 DSC曲线</t>
+  </si>
+  <si>
+    <t>Wang L, Zhao S, Li A, et al. Study on the structure and properties of SSBR with large-volume functional groups at the end of chains[J]. Polymer, 2010, 51(10): 2084-2090.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polymer.2010.03.006</t>
+  </si>
+  <si>
+    <t>SSBR-052</t>
+  </si>
+  <si>
+    <t>白炭黑填充 SSBR 复合材料</t>
+  </si>
+  <si>
+    <t>烷氧基硅烷</t>
+  </si>
+  <si>
+    <t>[Si](OC)(OC)(OC)C</t>
+  </si>
+  <si>
+    <t>[Si](OC)(OC)OC</t>
+  </si>
+  <si>
+    <t>烷氧基硅烷基</t>
+  </si>
+  <si>
+    <t>-Si(OR)3</t>
+  </si>
+  <si>
+    <t>[Si](OC)(OC)(OC)C-140000-19.4-48.5---[Si](OC)(OC)OC--</t>
+  </si>
+  <si>
+    <t>文献 Fig.7 应力-应变曲线</t>
+  </si>
+  <si>
+    <t>Liu X, Zhao S, Zhang X, et al. Preparation, structure, and properties of solution-polymerized styrene-butadiene rubber with functionalized end-groups and its silica-filled composites[J]. Polymer, 2014, 55(8): 1964-1976.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polymer.2014.02.067</t>
+  </si>
+  <si>
+    <t>SSBR-058</t>
+  </si>
+  <si>
+    <t>轮胎、密封件、减震器</t>
+  </si>
+  <si>
+    <t>2-巯基乙醇 (ME)</t>
+  </si>
+  <si>
+    <t>OCCS-395000-20.2-44.6-S-[OH]-7.8mol %</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 (示意)</t>
+  </si>
+  <si>
+    <t>文献 Fig.S4 (DMA)</t>
+  </si>
+  <si>
     <t>文献 Fig.3</t>
   </si>
   <si>
+    <t>Zhang X, Tang Z, Guo B. Regulation of mechanical properties of diene rubber cured by oxa-Michael Reaction via manipulating network structure[J]. Polymer, 2018, 145: 242-251.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polymer.2018.04.039</t>
+  </si>
+  <si>
+    <t>SSBR-061</t>
+  </si>
+  <si>
+    <t>汽车工业、白炭黑填充复合材料</t>
+  </si>
+  <si>
+    <t>3-(氨基丙基)三乙氧基硅烷 (APTES)</t>
+  </si>
+  <si>
+    <t>C1(OCC)[Si](OCC)(OCC)CCCN</t>
+  </si>
+  <si>
+    <t>-NH2</t>
+  </si>
+  <si>
+    <t>C1(OCC)[Si](OCC)(OCC)CCCN---25.0---[Si](OC)(OC)OC-N--</t>
+  </si>
+  <si>
+    <t>文献 Fig.1 (机理)</t>
+  </si>
+  <si>
+    <t>文献 Table 9</t>
+  </si>
+  <si>
+    <t>Hassanabadi M, Najafi M, Motlagh G H, et al. Synthesis and characterization of end-functionalized solution polymerized styrene-butadiene rubber and study the impact of silica dispersion improvement on the wear behavior of the composite[J]. Polymer Testing, 2020, 85: 106431.</t>
+  </si>
+  <si>
+    <t>10.1016/j.polymertesting.2020.106431</t>
+  </si>
+  <si>
+    <t>SSBR-062</t>
+  </si>
+  <si>
+    <t>甲酸、过氧化氢（原位生成过氧甲酸）</t>
+  </si>
+  <si>
+    <t>C(=O)OO</t>
+  </si>
+  <si>
+    <t>过氧羧基</t>
+  </si>
+  <si>
+    <t>mol%</t>
+  </si>
+  <si>
+    <t>C(=O)OO-396000-27.0-56.0-C(=O)OO-C1OC1-7mol%</t>
+  </si>
+  <si>
+    <t>文献 Fig.3b ¹H NMR谱图</t>
+  </si>
+  <si>
+    <t>文献 Fig.5 TEM图</t>
+  </si>
+  <si>
+    <t>文献 Fig.4 Payne效应曲线、文献 Fig.9 拉伸应力-应变曲线</t>
+  </si>
+  <si>
+    <t>文献 Fig.3c DSC曲线</t>
+  </si>
+  <si>
+    <t>Liu C, Guo M, Zhai X, et al. Using Epoxidized Solution Polymerized Styrene-Butadiene Rubbers (ESSBRs) as Coupling Agents to Modify Silica without Volatile Organic Compounds[J]. Polymers, 2020, 12(6): 1257.</t>
+  </si>
+  <si>
+    <t>10.3390/polym12061257</t>
+  </si>
+  <si>
+    <t>SSBR-064</t>
+  </si>
+  <si>
+    <t>绿色轮胎、抗湿滑与抗老化</t>
+  </si>
+  <si>
+    <t>对苯二胺 (PPD) 改性氧化石墨烯</t>
+  </si>
+  <si>
+    <t>C1=CC(=CC=C1N)N.[*]c1ccccc1O[*]</t>
+  </si>
+  <si>
+    <t>C1=CC(=CC=C1N)N.[*]c1ccccc1O[*]---------N--</t>
+  </si>
+  <si>
+    <t>Wan S, Lu X, Zhao H, et al. Effect of Graphene Oxide Modified with Organic Amine on the Aging Resistance, Rolling Loss and Wet-skid Resistance of Solution Polymerized Styrene-Butadiene Rubber[J]. Materials, 2020, 13(5): 1025.</t>
+  </si>
+  <si>
+    <t>10.3390/ma13051025</t>
+  </si>
+  <si>
+    <t>SSBR-065</t>
+  </si>
+  <si>
+    <t>形状记忆、自修复高强韧弹性体</t>
+  </si>
+  <si>
+    <t>三唑啉二酮 (TAD)</t>
+  </si>
+  <si>
+    <t>O=C1N=NC(=O)N1</t>
+  </si>
+  <si>
+    <t>碳碳双键</t>
+  </si>
+  <si>
+    <t>C=C</t>
+  </si>
+  <si>
+    <t>NC(=O)N</t>
+  </si>
+  <si>
+    <t>脲唑基</t>
+  </si>
+  <si>
+    <t>-NHCONH-</t>
+  </si>
+  <si>
+    <t>O=C1N=NC(=O)N1-------C=C-NC(=O)N--</t>
+  </si>
+  <si>
+    <t>Huang J, Zhang L, Tang Z, et al. Bioinspired Design of a Robust Elastomer with Adaptive Recovery via Triazolinedione Click Chemistry[J]. Macromolecular Rapid Communications, 2017.</t>
+  </si>
+  <si>
+    <t>10.1002/marc.201600678</t>
+  </si>
+  <si>
+    <t>SSBR-068</t>
+  </si>
+  <si>
+    <t>膨胀石墨/橡胶纳米复合材料</t>
+  </si>
+  <si>
+    <t>羧基化丁苯橡胶 (XSBR) 作为增容剂</t>
+  </si>
+  <si>
+    <t>C1=CC=CC=C1.C1=CC(CCC1C=C)C(=O)O</t>
+  </si>
+  <si>
+    <t>C1=CC=CC=C1.C1=CC(CCC1C=C)C(=O)O---------C(=O)O--</t>
+  </si>
+  <si>
+    <t>Malas A, Das C K. Development of Modified Expanded Graphite-Filled Solution Polymerized Styrene Butadiene Rubber Vulcanizates in the Presence and Absence of Carbon Black[J]. Polymer Engineering &amp; Science, 2014, 54: 33-41.</t>
+  </si>
+  <si>
+    <t>10.1002/pen.23533</t>
+  </si>
+  <si>
+    <t>SSBR-069</t>
+  </si>
+  <si>
+    <t>纳米白炭黑分散改性</t>
+  </si>
+  <si>
+    <t>二苯胍 (DPG)</t>
+  </si>
+  <si>
+    <t>c1ccc(NC(=Nc2ccccc2)N)cc1</t>
+  </si>
+  <si>
+    <t>NC(=Nc1ccccc1)Nc2ccccc2</t>
+  </si>
+  <si>
+    <t>胍基</t>
+  </si>
+  <si>
+    <t>-C(=NPh)(NHPh)</t>
+  </si>
+  <si>
+    <t>c1ccc(NC(=Nc2ccccc2)N)cc1---------NC(=Nc1ccccc1)Nc2ccccc2--</t>
+  </si>
+  <si>
+    <t>Mao Y, Tian Q, Zhang C, et al. Vulcanization Accelerator Functionalized Nanosilica: Effect on the Reinforcement Behavior of SSBR/BR[J]. Polymer Engineering &amp; Science, 2019.</t>
+  </si>
+  <si>
+    <t>10.1002/pen.25110</t>
+  </si>
+  <si>
+    <t>SSBR-071</t>
+  </si>
+  <si>
+    <t>白炭黑/SSBR 混炼界面偶联</t>
+  </si>
+  <si>
+    <t>Si747 (硅烷偶联剂)</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSSSCCCO[Si](OCC)(OCC)OCC)(OCC)OCC</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSSSCCCO[Si](OCC)(OCC)OCC)(OCC)OCC---------[Si](OCC)(OCC)OCC--</t>
+  </si>
+  <si>
+    <t>Tao Y C, Dong B, Zhang L Q, et al. REACTIONS OF SILICA-SILANE RUBBER AND PROPERTIES OF SILANE-SILICA/SOLUTION-POLYMERIZED STYRENE-BUTADIENE RUBBER COMPOSITE[J]. Rubber Chemistry and Technology, 2016, 89(3): 526-539.</t>
+  </si>
+  <si>
+    <t>10.5254/rct.16.84812</t>
+  </si>
+  <si>
+    <t>SSBR-075</t>
+  </si>
+  <si>
+    <t>轮胎胎面胶硅烷化研究</t>
+  </si>
+  <si>
+    <t>TESPT</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSSSCCCC[Si](OCC)(OCC)OCC)(OCC)OCC</t>
+  </si>
+  <si>
+    <t>硅烷基</t>
+  </si>
+  <si>
+    <t>CCO[Si](CCCSSSSCCCC[Si](OCC)(OCC)OCC)(OCC)OCC---------[Si](OCC)(OCC)OCC--</t>
+  </si>
+  <si>
+    <t>Jin J, Noordermeer J W M, Dierkes W K, et al. The Effect of Silanization Temperature and Time on the Marching Modulus of Silica-Filled Tire Tread Compounds[J]. Polymers, 2020, 12(1): 209.</t>
+  </si>
+  <si>
+    <t>10.3390/polym12010209</t>
+  </si>
+  <si>
+    <t>SSBR-076</t>
+  </si>
+  <si>
+    <t>绿色轮胎、白炭黑改性</t>
+  </si>
+  <si>
+    <t>间氯过氧苯甲酸 (m-CPBA)</t>
+  </si>
+  <si>
+    <t>Clc1cccc(C(=O)OO)c1</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Clc1cccc(C(=O)OO)c1-100000-21.0-63.0---C1OC1-7%</t>
+  </si>
+  <si>
+    <t>文献 Fig.11</t>
+  </si>
+  <si>
+    <t>SSBR-078</t>
+  </si>
+  <si>
+    <t>生物基橡胶、高性能轮胎</t>
+  </si>
+  <si>
+    <t>CC(=C)C=CC=C(C)C</t>
+  </si>
+  <si>
+    <t>萜烯基</t>
+  </si>
+  <si>
+    <t>-萜烯-</t>
+  </si>
+  <si>
+    <t>CC(C)=CCCC(=C)C=C-246000-------CC(=C)C=CC=C(C)C--</t>
+  </si>
+  <si>
+    <t>文献 Fig.6 TEM图</t>
+  </si>
+  <si>
+    <t>Zhang J, Lu J, Wang D, et al. Preparation, carbon black dispersibility and performances of novel biobased integral solution-polymerized styrene-butadiene rubber with β-myrcene bottlebrush segments[J]. Journal of Materials Science, 2020, 55.</t>
+  </si>
+  <si>
+    <t>10.1007/s10853-020-05218-w</t>
+  </si>
+  <si>
+    <t>SSBR-079</t>
+  </si>
+  <si>
+    <t>EVA 改性白炭黑</t>
+  </si>
+  <si>
+    <t>C1=CC(=O)OC1.CC(=O)O.[O-][Si]([O-])([O-])[O-]</t>
+  </si>
+  <si>
+    <t>CC(=O)OC=C</t>
+  </si>
+  <si>
+    <t>酯基/乙烯基</t>
+  </si>
+  <si>
+    <t>-OCOCH₃/-CH=CH₂</t>
+  </si>
+  <si>
+    <t>C1=CC(=O)OC1.CC(=O)O.[O-][Si]([O-])([O-])[O-]---------CC(=O)OC=C--</t>
+  </si>
+  <si>
     <t>文献 Fig.4</t>
-  </si>
-  <si>
-    <t>文献 Fig.5</t>
-  </si>
-  <si>
-    <t>Huang M, et al. [J]. Ind. Eng. Chem. Res. 2016, 55(34): 9190-9198.</t>
-  </si>
-  <si>
-    <t>SSBR-017</t>
-  </si>
-  <si>
-    <t>硅橡胶/SSBR界面改性</t>
-  </si>
-  <si>
-    <t>TMPMP</t>
-  </si>
-  <si>
-    <t>OCC(C)(COC(=O)CCS)COC(=O)CCS</t>
-  </si>
-  <si>
-    <t>C(=O)OCC</t>
-  </si>
-  <si>
-    <t>酯基</t>
-  </si>
-  <si>
-    <t>-COOR</t>
-  </si>
-  <si>
-    <t>OCC(C)(COC(=O)CCS)COC(=O)CCS---23.5---S-C(=O)OCC--</t>
-  </si>
-  <si>
-    <t>文献 Fig.6</t>
-  </si>
-  <si>
-    <t>Sun Z, et al. [J]. Ind. Eng. Chem. Res. 2017, 56(6): 1471-1477.</t>
-  </si>
-  <si>
-    <t>10.1021/acs.iecr.6b04146</t>
-  </si>
-  <si>
-    <t>SSBR-018</t>
-  </si>
-  <si>
-    <t>二氧化硅分散</t>
-  </si>
-  <si>
-    <t>DPE-NMe2</t>
-  </si>
-  <si>
-    <t>CN(C)c1ccc(C(=C)c2ccccc2)cc1</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>氨基</t>
-  </si>
-  <si>
-    <t>-NMe2</t>
-  </si>
-  <si>
-    <t>CN(C)c1ccc(C(=C)c2ccccc2)cc1---------N--</t>
-  </si>
-  <si>
-    <t>文献 Fig.1</t>
-  </si>
-  <si>
-    <t>Sun C, et al. [J]. Ind. Eng. Chem. Res. 2019, 58.</t>
-  </si>
-  <si>
-    <t>10.1021/acs.iecr.8b05738</t>
-  </si>
-  <si>
-    <t>SSBR-019</t>
-  </si>
-  <si>
-    <t>SSBR-020</t>
-  </si>
-  <si>
-    <t>CCC(COC(=O)CCS)(COC(=O)CCS)COC(=O)CCS</t>
-  </si>
-  <si>
-    <t>CCC(COC(=O)CCS)(COC(=O)CCS)COC(=O)CCS---23.5---S-C(=O)OCC--</t>
-  </si>
-  <si>
-    <t>Sun Z, Huang Q, Wang Y, et al. Structure and Properties of Silicone Rubber/Styrene−Butadiene Rubber Blends with in Situ Interface Coupling by Thiol-ene Click Reaction[J]. Industrial &amp; Engineering Chemistry Research, 2017, 56(6): 1471-1477.</t>
-  </si>
-  <si>
-    <t>SSBR-021</t>
-  </si>
-  <si>
-    <t>Sun C, Shipeng W, Ma H, et al. Improvement of silica dispersion in solution polymerized styrene-butadiene rubber via introducing amino functional groups[J]. Industrial &amp; Engineering Chemistry Research, 2019, 58(2): 586-592.</t>
-  </si>
-  <si>
-    <t>SSBR-022</t>
-  </si>
-  <si>
-    <t>石墨烯/橡胶复合材料</t>
-  </si>
-  <si>
-    <t>TPES</t>
-  </si>
-  <si>
-    <t>C=Cc1ccc(CC(c2ccccc2)(c3ccccc3)c4ccccc4)cc1</t>
-  </si>
-  <si>
-    <t>c1ccc(C(c2ccccc2)(c3ccccc3)c4ccccc4)cc1</t>
-  </si>
-  <si>
-    <t>三苯基乙基</t>
-  </si>
-  <si>
-    <t>-CPh3</t>
-  </si>
-  <si>
-    <t>C=Cc1ccc(CC(c2ccccc2)(c3ccccc3)c4ccccc4)cc1-168000-24.0-----c1ccc(C(c2ccccc2)(c3ccccc3)c4ccccc4)cc1-0.9wt%</t>
-  </si>
-  <si>
-    <t>Huang M, Lu J, Han B, et al. Covalent approach for in situ enhancement of interaction between pristine graphene and styrene-butadiene-p-(2,2,2-triphenylethyl)styrene rubber[J]. Journal of Applied Polymer Science, 2017, 134(28): 44923.</t>
-  </si>
-  <si>
-    <t>10.1002/app.44923</t>
-  </si>
-  <si>
-    <t>SSBR-023</t>
-  </si>
-  <si>
-    <t>二氧化硅填料分散</t>
-  </si>
-  <si>
-    <t>3-巯基丙酸(3-MPA)</t>
-  </si>
-  <si>
-    <t>SCCC(=O)O</t>
-  </si>
-  <si>
-    <t>mol %</t>
-  </si>
-  <si>
-    <t>SCCC(=O)O-223900-23.4-47.3-S-C(=O)O-1.7mol %</t>
-  </si>
-  <si>
-    <t>文献 Fig.10</t>
-  </si>
-  <si>
-    <t>文献 Fig.12</t>
-  </si>
-  <si>
-    <t>Wang L, Lu Y, Xie X, et al. In situ grafting onto solution polymerized styrene butadiene rubbers (SSBR) filled with silica via solid state method[J]. Journal of Applied Polymer Science, 2018, 135(34): 46653.</t>
-  </si>
-  <si>
-    <t>10.1002/app.46653</t>
-  </si>
-  <si>
-    <t>SSBR-024</t>
-  </si>
-  <si>
-    <t>MMP</t>
-  </si>
-  <si>
-    <t>Cn1cc[nH+]c1.SCCC(=O)[O-]</t>
-  </si>
-  <si>
-    <t>C[n+]1ccn(C)c1</t>
-  </si>
-  <si>
-    <t>咪唑鎓</t>
-  </si>
-  <si>
-    <t>-Im+</t>
-  </si>
-  <si>
-    <t>Cn1cc[nH+]c1.SCCC(=O)[O-]---27.0---S-C[n+]1ccn(C)c1-14.8mol %</t>
-  </si>
-  <si>
-    <t>文献 Fig.7</t>
-  </si>
-  <si>
-    <t>Weng P, Tang Z, Huang J, et al. Promoted dispersion of silica and interfacial strength in rubber/silica composites by grafting with oniums[J]. Journal of Applied Polymer Science, 2019, 136(44): 48243.</t>
-  </si>
-  <si>
-    <t>10.1002/app.48243</t>
-  </si>
-  <si>
-    <t>SSBR-025</t>
-  </si>
-  <si>
-    <t>轮胎胎面胶</t>
-  </si>
-  <si>
-    <t>丙胺, 二甲氧基硅烷</t>
-  </si>
-  <si>
-    <t>NCC.CO[SiH](OC)C</t>
-  </si>
-  <si>
-    <t>N.[Si](O)(O)O</t>
-  </si>
-  <si>
-    <t>氨基/硅烷基</t>
-  </si>
-  <si>
-    <t>-NH2/-Si(OR)3</t>
-  </si>
-  <si>
-    <t>NCC.CO[SiH](OC)C---36.0-26.0---N.[Si](O)(O)O--</t>
-  </si>
-  <si>
-    <t>文献 Table III</t>
-  </si>
-  <si>
-    <t>Sirisinha C, Sae-oui P, Suchiva K, et al. Properties of tire tread compounds based on functionalized styrene butadiene rubber and functionalized natural rubber[J]. Journal of Applied Polymer Science, 2019, 137(13): 48696.</t>
-  </si>
-  <si>
-    <t>10.1002/app.48696</t>
-  </si>
-  <si>
-    <t>SSBR-026</t>
-  </si>
-  <si>
-    <t>β-月桂烯</t>
-  </si>
-  <si>
-    <t>CC(C)=CCCC(=C)C=C</t>
-  </si>
-  <si>
-    <t>CC(C)</t>
-  </si>
-  <si>
-    <t>异亚丙基侧链</t>
-  </si>
-  <si>
-    <t>-C(CH3)2-</t>
-  </si>
-  <si>
-    <t>CC(C)=CCCC(=C)C=C-150000-------CC(C)--</t>
-  </si>
-  <si>
-    <t>Zhang J, Lu J, Su K, et al. Bio-based β-myrcene-modiﬁed solution-polymerized styrene-butadiene rubber for improving carbon black dispersion and wet skid resistance[J]. Journal of Applied Polymer Science, 2019, 136(30): 48159.</t>
-  </si>
-  <si>
-    <t>10.1002/app.48159</t>
-  </si>
-  <si>
-    <t>SSBR-030</t>
-  </si>
-  <si>
-    <t>3-巯基丙酸 (3-MPA)</t>
-  </si>
-  <si>
-    <t>SCCC(=O)O-206600-21.0---S-C(=O)O-2.4wt%</t>
-  </si>
-  <si>
-    <t>文献 Fig.8 TEM图</t>
-  </si>
-  <si>
-    <t>文献 Fig.2 Payne效应</t>
-  </si>
-  <si>
-    <t>文献 Fig.11 DSC曲线</t>
-  </si>
-  <si>
-    <t>Qu L, Zhang W, Yang H, et al. Contribution of silica interaction with functionalized SSBR on the performance of green tire tread compounds[J]. RSC Advances, 2014, 4(109): 64354-64362.</t>
-  </si>
-  <si>
-    <t>10.1039/c4ra09492a</t>
-  </si>
-  <si>
-    <t>SSBR-031</t>
-  </si>
-  <si>
-    <t>绿色轮胎、高分散白炭黑复合材料</t>
-  </si>
-  <si>
-    <t>SCCC(=O)O-214700-20.7---S-C(=O)O-2.4wt%</t>
-  </si>
-  <si>
-    <t>文献 Fig.7 TEM图</t>
-  </si>
-  <si>
-    <t>Luo Y, Qu L, Su H, et al. Effect of chemical structure of elastomer on filler dispersion and interactions in silica/solution-polymerized styrene butadiene rubber composites through molecular dynamics simulation[J]. RSC Advances, 2016, 6(17): 14643-14650.</t>
-  </si>
-  <si>
-    <t>10.1039/c5ra24965a</t>
-  </si>
-  <si>
-    <t>SSBR-033</t>
-  </si>
-  <si>
-    <t>高性能轮胎、节能环保轮胎</t>
-  </si>
-  <si>
-    <t>1,5-萘二异氰酸酯 (NDI)</t>
-  </si>
-  <si>
-    <t>O=C=Nc1ccc2c(N=C=O)ccc12</t>
-  </si>
-  <si>
-    <t>异氰酸根</t>
-  </si>
-  <si>
-    <t>N=C=O</t>
-  </si>
-  <si>
-    <t>NC(=O)O</t>
-  </si>
-  <si>
-    <t>聚氨酯硬段</t>
-  </si>
-  <si>
-    <t>-NHCOO-</t>
-  </si>
-  <si>
-    <t>O=C=Nc1ccc2c(N=C=O)ccc12-------N=C=O-NC(=O)O--</t>
-  </si>
-  <si>
-    <t>文献 Fig.7 SEM图</t>
-  </si>
-  <si>
-    <t>文献 Table 1</t>
-  </si>
-  <si>
-    <t>Qin X, Wang J, Han B, et al. Novel Design of Eco-Friendly Super Elastomer Materials With Optimized Hard Segments Micro-Structure: Toward Next-Generation High-Performance Tires[J]. Frontiers in Chemistry, 2018, 6: 240.</t>
-  </si>
-  <si>
-    <t>10.3389/fchem.2018.00240</t>
-  </si>
-  <si>
-    <t>SSBR-034</t>
-  </si>
-  <si>
-    <t>超疏水涂层、输送带</t>
-  </si>
-  <si>
-    <t>三羟甲基丙烷三(3-巯基丙酸)酯 (TMPMP)</t>
-  </si>
-  <si>
-    <t>CCC(COC(=O)CCS)(COC(=O)CCS)COC(=O)CCS-160200-----S-C(=O)OCC-10wt%</t>
-  </si>
-  <si>
-    <t>文献 Fig.S1</t>
-  </si>
-  <si>
-    <t>文献 Fig.5 SEM图</t>
-  </si>
-  <si>
-    <t>文献 Fig.7 粘附力曲线</t>
-  </si>
-  <si>
-    <t>Ning N, Wang S, Zhang Z, et al. Superhydrophobic coating with Ultrahigh Adhesive Force and Good Anti-scratching on Elastomeric Substrate by Thiol-ene Click Chemistry[J]. Chemical Engineering Journal, 2019, 370: 1100-1108.</t>
-  </si>
-  <si>
-    <t>10.1016/j.cej.2019.04.215</t>
-  </si>
-  <si>
-    <t>SSBR-036</t>
-  </si>
-  <si>
-    <t>绿色轮胎</t>
-  </si>
-  <si>
-    <t>双环氧丙基多硫化物 (BEP)</t>
-  </si>
-  <si>
-    <t>C1OC1CSSSSCC2CO2</t>
-  </si>
-  <si>
-    <t>C1OC1</t>
-  </si>
-  <si>
-    <t>环氧基</t>
-  </si>
-  <si>
-    <t>-C2H2O-</t>
-  </si>
-  <si>
-    <t>C1OC1CSSSSCC2CO2---25.0-50.0---C1OC1--</t>
-  </si>
-  <si>
-    <t>文献 Fig.11 损耗因子</t>
-  </si>
-  <si>
-    <t>Ye N, Zheng J, Xin Y, et al. Performance enhancement of rubber composites using VOC-Free interfacial silica coupling agent[J]. Composites Part B: Engineering, 2020, 202: 108301.</t>
-  </si>
-  <si>
-    <t>10.1016/j.compositesb.2020.108301</t>
-  </si>
-  <si>
-    <t>SSBR-038</t>
-  </si>
-  <si>
-    <t>气体阻隔材料、复合材料</t>
-  </si>
-  <si>
-    <t>1-庚硫醇、1-十八烷硫醇</t>
-  </si>
-  <si>
-    <t>CCCCCCC S</t>
-  </si>
-  <si>
-    <t>CCCCCC</t>
-  </si>
-  <si>
-    <t>烷基链</t>
-  </si>
-  <si>
-    <t>-(CH2)n-</t>
-  </si>
-  <si>
-    <t>CCCCCCC S---25.0-50.0-S-CCCCCC--</t>
-  </si>
-  <si>
-    <t>文献 Fig.7 存储模量</t>
-  </si>
-  <si>
-    <t>Luo Y, Wu Y, Luo K, et al. Structures and properties of alkanethiol-modified graphene oxide/solution-polymerized styrene butadiene rubber composites: Click chemistry and molecular dynamics simulation[J]. Composites Science and Technology, 2018, 161: 32-38.</t>
-  </si>
-  <si>
-    <t>10.1016/j.compscitech.2018.03.036</t>
-  </si>
-  <si>
-    <t>SSBR-040</t>
-  </si>
-  <si>
-    <t>轮胎、高耐磨复合材料</t>
-  </si>
-  <si>
-    <t>六甲基二硅氮烷 (HMDS)</t>
-  </si>
-  <si>
-    <t>CC[Si](C)(C)N[Si](C)(C)C</t>
-  </si>
-  <si>
-    <t>硅氮基</t>
-  </si>
-  <si>
-    <t>[Si]N</t>
-  </si>
-  <si>
-    <t>[Si](C)(C)C</t>
-  </si>
-  <si>
-    <t>三甲基硅基</t>
-  </si>
-  <si>
-    <t>-Si(CH3)3</t>
-  </si>
-  <si>
-    <t>CC[Si](C)(C)N[Si](C)(C)C---25.0-50.0-[Si]N-[Si](C)(C)C--</t>
-  </si>
-  <si>
-    <t>文献 Fig.11 SEM图</t>
-  </si>
-  <si>
-    <t>文献 Fig.8 拉伸强度</t>
-  </si>
-  <si>
-    <t>Tian Q, Zhang C, Tang Y, et al. Preparation of hexamethyl disilazane-surface functionalized nano-silica by controlling surface chemistry and its “agglomeration-collapse” behavior in solution polymerized styrene butadiene rubber/butadiene rubber composites[J]. Composites Science and Technology, 2021, 201: 108482.</t>
-  </si>
-  <si>
-    <t>10.1016/j.compscitech.2020.108482</t>
-  </si>
-  <si>
-    <t>SSBR-041</t>
-  </si>
-  <si>
-    <t>高性能抗老化轮胎</t>
-  </si>
-  <si>
-    <t>N-(4-苯胺基苯基)马来酰亚胺 (MC)</t>
-  </si>
-  <si>
-    <t>O=C1C=CC(=O)N1c2ccc(Nc3ccccc3)cc2</t>
-  </si>
-  <si>
-    <t>马来酰亚胺基</t>
-  </si>
-  <si>
-    <t>N1C(=O)C=CC1=O</t>
-  </si>
-  <si>
-    <t>Nc1ccc(N)cc1</t>
-  </si>
-  <si>
-    <t>对苯二胺衍生物</t>
-  </si>
-  <si>
-    <t>-C6H4(NH2)2</t>
-  </si>
-  <si>
-    <t>O=C1C=CC(=O)N1c2ccc(Nc3ccccc3)cc2---25.0-50.0-N1C(=O)C=CC1=O-Nc1ccc(N)cc1--</t>
-  </si>
-  <si>
-    <t>文献 Fig.10 TEM图</t>
-  </si>
-  <si>
-    <t>文献 Fig.7 拉伸曲线</t>
-  </si>
-  <si>
-    <t>Luo K, Zheng W, Zhao X, et al. Effects of antioxidant functionalized silica on reinforcement and anti-aging for solution-polymerized styrene butadiene rubber: Experimental and molecular simulation study[J]. Materials &amp; Design, 2018, 154: 114-125.</t>
-  </si>
-  <si>
-    <t>10.1016/j.matdes.2018.05.048</t>
-  </si>
-  <si>
-    <t>SSBR-042</t>
-  </si>
-  <si>
-    <t>绿色轮胎胎面材料</t>
-  </si>
-  <si>
-    <t>[3-(2-氨基乙基)氨基丙基]三甲氧基硅烷（AMMO）</t>
-  </si>
-  <si>
-    <t>COC[Si](CCC(NCCN)OC)(OC)OC</t>
-  </si>
-  <si>
-    <t>N.[Si](OC)(OC)OC</t>
-  </si>
-  <si>
-    <t>氨基/三甲氧基硅烷基</t>
-  </si>
-  <si>
-    <t>-NH2/-Si(OCH₃)₃</t>
-  </si>
-  <si>
-    <t>COC[Si](CCC(NCCN)OC)(OC)OC-258000-21.1-38.1---N.[Si](OC)(OC)OC--</t>
-  </si>
-  <si>
-    <t>文献 Fig.1 共凝聚橡胶的TEM照片；文献 Fig.7 SSBR/SiO2和N-SSBR/SiO2纳米复合材料的TEM照片</t>
-  </si>
-  <si>
-    <t>文献 Fig.5 SSBR/SiO2和N-SSBR/SiO2纳米复合材料的G'-应变曲线；文献 Fig.6 SSBR/SiO2和N-SSBR/SiO2纳米复合材料的tanδ-应变曲线</t>
-  </si>
-  <si>
-    <t>文献 Fig.3 生胶和共凝聚橡胶的G'-T和tanδ-T曲线；文献 Fig.4 SSBR/SiO2和N-SSBR/SiO2纳米复合材料的G'-T和tanδ-T曲线</t>
-  </si>
-  <si>
-    <t>Liu X, Zhao S H. Study on Structure and Properties of SSBR/SiO2 Co-coagulated Rubber and SSBR Filled with Nanosilica Composites[J]. Journal of Applied Polymer Science, 2008, 109(6): 3900-3907.</t>
-  </si>
-  <si>
-    <t>10.1002/app.28621</t>
-  </si>
-  <si>
-    <t>SSBR-043</t>
-  </si>
-  <si>
-    <t>COC[Si](CCC(NCCN)OC)(OC)OC-336000-24.2-46.0---N.[Si](OC)(OC)OC--</t>
-  </si>
-  <si>
-    <t>SSBR-044</t>
-  </si>
-  <si>
-    <t>COC[Si](CCC(NCCN)OC)(OC)OC-351000-29.5-34.7---N.[Si](OC)(OC)OC--</t>
-  </si>
-  <si>
-    <t>SSBR-045</t>
-  </si>
-  <si>
-    <t>轮胎胎面</t>
-  </si>
-  <si>
-    <t>3-辛酰硫基-1-丙基三乙氧基硅烷</t>
-  </si>
-  <si>
-    <t>CCCCCCCC(=O)SCCC[Si](OCC)(OCC)OCC</t>
-  </si>
-  <si>
-    <t>CCCCCCCC(=O)SCCC[Si](OCC)(OCC)OCC---25.0-----[Si](OCC)(OCC)OCC--</t>
-  </si>
-  <si>
-    <t>文献 Fig.1 不同填料含量的SiO2/SSBR复合材料在不同γ值下的G(t,γ)随时间t变化曲线；文献 Fig.3 不同填料含量的SiO2/SSBR复合材料的h(γ)随γ变化曲线</t>
-  </si>
-  <si>
-    <t>Sun J, Li H, Song Y H, et al. Nonlinear Stress Relaxation of Silica Filled Solution-Polymerized Styrene–Butadiene Rubber Compounds[J]. Journal of Applied Polymer Science, 2009, 112(6): 3569-3574.</t>
-  </si>
-  <si>
-    <t>10.1002/app.29646</t>
-  </si>
-  <si>
-    <t>SSBR-046</t>
-  </si>
-  <si>
-    <t>双[γ-(三乙氧基硅基)丙基]二硫化物（Si-75）</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC</t>
-  </si>
-  <si>
-    <t>[Si](OCC)(OCC)OCC.SS</t>
-  </si>
-  <si>
-    <t>三乙氧基硅烷基/二硫化物</t>
-  </si>
-  <si>
-    <t>-Si(OC₂H₅)₃/-S-S-</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC-123000-27.5-25.4---[Si](OCC)(OCC)OCC.SS--</t>
-  </si>
-  <si>
-    <t>文献 Fig.3 SSBR/SiO2/CB纳米复合材料的TEM照片</t>
-  </si>
-  <si>
-    <t>文献 Fig.4 SSBR/SiO2/CB纳米复合材料的G'-应变和tanδ-应变曲线</t>
-  </si>
-  <si>
-    <t>文献 Fig.4 SSBR/SiO2/CB纳米复合材料的tanδ-温度曲线</t>
-  </si>
-  <si>
-    <t>Wang L, Zhao S H. Study on the Structure-Mechanical Properties Relationship and Antistatic Characteristics of SSBR Composites Filled with SiO2/CB[J]. Journal of Applied Polymer Science, 2010, 118(1): 338-345.</t>
-  </si>
-  <si>
-    <t>10.1002/app.32372</t>
-  </si>
-  <si>
-    <t>SSBR-047</t>
-  </si>
-  <si>
-    <t>绿色轮胎胎面</t>
-  </si>
-  <si>
-    <t>双-(三乙氧基硅基丙基)-四硫化物（TESPT）、双-(三乙氧基硅基丙基)-二硫化物（TESPD）</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC</t>
-  </si>
-  <si>
-    <t>[Si](OCC)(OCC)OCC.SSSS</t>
-  </si>
-  <si>
-    <t>三乙氧基硅烷基/多硫化物</t>
-  </si>
-  <si>
-    <t>-Si(OC₂H₅)₃/-Sₓ-</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC-167000-24.8-9.7---[Si](OCC)(OCC)OCC.SSSS--</t>
-  </si>
-  <si>
-    <t>文献 Fig.1 未改性二氧化硅和硅烷改性二氧化硅的FTIR谱图</t>
-  </si>
-  <si>
-    <t>文献 Fig.2 SSBR/二氧化硅纳米复合材料的TEM照片</t>
-  </si>
-  <si>
-    <t>文献 Fig.5 填充SSBR的储能模量-动态应变曲线；文献 Fig.7 填充SSBR的应力-应变曲线</t>
-  </si>
-  <si>
-    <t>文献 Fig.8 填充SSBR的储能模量-温度曲线、损耗因子-温度曲线</t>
-  </si>
-  <si>
-    <t>Qu L L, Yu G Z, Wang L L, et al. Effect of Filler–Elastomer Interactions on the Mechanical and Nonlinear Viscoelastic Behaviors of Chemically Modified Silica-Reinforced Solution-Polymerized Styrene Butadiene Rubber[J]. Journal of Applied Polymer Science, 2012, 125(2): 1174-1184.</t>
-  </si>
-  <si>
-    <t>10.1002/app.36677</t>
-  </si>
-  <si>
-    <t>SSBR-048</t>
-  </si>
-  <si>
-    <t>[3-(2-氨基乙基)氨基丙基]三甲氧基硅烷</t>
-  </si>
-  <si>
-    <t>文献 Fig.2 N-SSBR的¹H NMR谱图</t>
-  </si>
-  <si>
-    <t>文献 Fig.3 N-SSBR和SSBR/SiO2/CB纳米复合材料的TEM照片；文献 Fig.6 硫化胶弯曲断裂表面的SEM照片</t>
-  </si>
-  <si>
-    <t>文献 Fig.4 SSBR/SiO2/CB和N-SSBR/SiO2/CB纳米复合材料的G'-应变和tanδ-应变曲线</t>
-  </si>
-  <si>
-    <t>Liu X, Zhao S H, Yang Y, et al. Dynamic Properties of Star-Shaped, Solution-Polymerized Styrene–Butadiene Rubber and Its Cocoagulated Rubber-Filled with Silica/Carbon Black[J]. Journal of Applied Polymer Science, 2014, 131(11): 40348.</t>
-  </si>
-  <si>
-    <t>10.1002/app.40348</t>
-  </si>
-  <si>
-    <t>SSBR-049</t>
-  </si>
-  <si>
-    <t>乘用车轮胎胎面胶</t>
-  </si>
-  <si>
-    <t>双-(3-(三乙氧基硅基)-丙基)-四硫化物（TESPT，Si-69）</t>
-  </si>
-  <si>
-    <t>三乙氧基硅烷基/四硫化物</t>
-  </si>
-  <si>
-    <t>-Si(OC₂H₅)₃/-S₄-</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSSSCCC[Si](OCC)(OCC)OCC)(OCC)OCC---34.6-40.1---[Si](OCC)(OCC)OCC.SSSS--</t>
-  </si>
-  <si>
-    <t>文献 Fig.4 不同硅烷化温度下二氧化硅填充硫化胶的TEM照片</t>
-  </si>
-  <si>
-    <t>文献 Fig.7 0℃下硫化胶损耗因子随动态应变的变化曲线；文献 Fig.8 60℃下硫化胶损耗因子随动态应变的变化曲线</t>
-  </si>
-  <si>
-    <t>文献 Fig.6 不同硅烷化温度下硫化胶的损耗因子(tanδ)随测试温度的变化曲线</t>
-  </si>
-  <si>
-    <t>Thaptong P, Sae-Oui P, Sirisinha C. Effects of silanization temperature and silica type on properties of silica-filled solution styrene butadiene rubber (SSBR) for passenger car tire tread compounds[J]. Journal of Applied Polymer Science, 2016, 133(17): 43342.</t>
-  </si>
-  <si>
-    <t>10.1002/app.43342</t>
-  </si>
-  <si>
-    <t>SSBR-050</t>
-  </si>
-  <si>
-    <t>极低滚阻节能轮胎</t>
-  </si>
-  <si>
-    <t>环氧乙烷</t>
-  </si>
-  <si>
-    <t>C1CO1</t>
-  </si>
-  <si>
-    <t>[OH]</t>
-  </si>
-  <si>
-    <t>C1CO1---------[OH]--</t>
-  </si>
-  <si>
-    <t>文献 Fig.9 损耗因子</t>
-  </si>
-  <si>
-    <t>文献 Fig.15 DSC曲线</t>
-  </si>
-  <si>
-    <t>Qin X, Han B, Lu J, et al. Rational Design of Advanced Elastomer Nanocomposites Towards Extremely Energy-saving Tires Based on Macromolecular Assembly Strategy[J]. Nano Energy, 2018, 48: 180-188.</t>
-  </si>
-  <si>
-    <t>10.1016/j.nanoen.2018.03.038</t>
-  </si>
-  <si>
-    <t>SSBR-051</t>
-  </si>
-  <si>
-    <t>炭黑填充 SSBR 复合材料</t>
-  </si>
-  <si>
-    <t>叔丁基氯二苯基硅烷 (TBCSi)</t>
-  </si>
-  <si>
-    <t>CC(C)(C)[Si](Cl)(c1ccccc1)c2ccccc2</t>
-  </si>
-  <si>
-    <t>[Si]</t>
-  </si>
-  <si>
-    <t>硅基</t>
-  </si>
-  <si>
-    <t>-SiR3</t>
-  </si>
-  <si>
-    <t>CC(C)(C)[Si](Cl)(c1ccccc1)c2ccccc2---------[Si]--</t>
-  </si>
-  <si>
-    <t>文献 Fig.1 ¹H NMR谱图</t>
-  </si>
-  <si>
-    <t>文献 Fig.5 损耗因子</t>
-  </si>
-  <si>
-    <t>文献 Fig.3 DSC曲线</t>
-  </si>
-  <si>
-    <t>Wang L, Zhao S, Li A, et al. Study on the structure and properties of SSBR with large-volume functional groups at the end of chains[J]. Polymer, 2010, 51(10): 2084-2090.</t>
-  </si>
-  <si>
-    <t>10.1016/j.polymer.2010.03.006</t>
-  </si>
-  <si>
-    <t>SSBR-052</t>
-  </si>
-  <si>
-    <t>白炭黑填充 SSBR 复合材料</t>
-  </si>
-  <si>
-    <t>烷氧基硅烷</t>
-  </si>
-  <si>
-    <t>[Si](OC)(OC)(OC)C</t>
-  </si>
-  <si>
-    <t>[Si](OC)(OC)OC</t>
-  </si>
-  <si>
-    <t>烷氧基硅烷基</t>
-  </si>
-  <si>
-    <t>-Si(OR)3</t>
-  </si>
-  <si>
-    <t>[Si](OC)(OC)(OC)C-140000-19.4-48.5---[Si](OC)(OC)OC--</t>
-  </si>
-  <si>
-    <t>文献 Fig.7 应力-应变曲线</t>
-  </si>
-  <si>
-    <t>Liu X, Zhao S, Zhang X, et al. Preparation, structure, and properties of solution-polymerized styrene-butadiene rubber with functionalized end-groups and its silica-filled composites[J]. Polymer, 2014, 55(8): 1964-1976.</t>
-  </si>
-  <si>
-    <t>10.1016/j.polymer.2014.02.067</t>
-  </si>
-  <si>
-    <t>SSBR-058</t>
-  </si>
-  <si>
-    <t>轮胎、密封件、减震器</t>
-  </si>
-  <si>
-    <t>2-巯基乙醇 (ME)</t>
-  </si>
-  <si>
-    <t>OCCS-395000-20.2-44.6-S-[OH]-7.8mol %</t>
-  </si>
-  <si>
-    <t>文献 Fig.1 (示意)</t>
-  </si>
-  <si>
-    <t>文献 Fig.S4 (DMA)</t>
-  </si>
-  <si>
-    <t>Zhang X, Tang Z, Guo B. Regulation of mechanical properties of diene rubber cured by oxa-Michael Reaction via manipulating network structure[J]. Polymer, 2018, 145: 242-251.</t>
-  </si>
-  <si>
-    <t>10.1016/j.polymer.2018.04.039</t>
-  </si>
-  <si>
-    <t>SSBR-061</t>
-  </si>
-  <si>
-    <t>汽车工业、白炭黑填充复合材料</t>
-  </si>
-  <si>
-    <t>3-(氨基丙基)三乙氧基硅烷 (APTES)</t>
-  </si>
-  <si>
-    <t>C1(OCC)[Si](OCC)(OCC)CCCN</t>
-  </si>
-  <si>
-    <t>-NH2</t>
-  </si>
-  <si>
-    <t>C1(OCC)[Si](OCC)(OCC)CCCN---25.0---[Si](OC)(OC)OC-N--</t>
-  </si>
-  <si>
-    <t>文献 Fig.1 (机理)</t>
-  </si>
-  <si>
-    <t>文献 Table 9</t>
-  </si>
-  <si>
-    <t>Hassanabadi M, Najafi M, Motlagh G H, et al. Synthesis and characterization of end-functionalized solution polymerized styrene-butadiene rubber and study the impact of silica dispersion improvement on the wear behavior of the composite[J]. Polymer Testing, 2020, 85: 106431.</t>
-  </si>
-  <si>
-    <t>10.1016/j.polymertesting.2020.106431</t>
-  </si>
-  <si>
-    <t>SSBR-062</t>
-  </si>
-  <si>
-    <t>甲酸、过氧化氢（原位生成过氧甲酸）</t>
-  </si>
-  <si>
-    <t>C(=O)OO</t>
-  </si>
-  <si>
-    <t>过氧羧基</t>
-  </si>
-  <si>
-    <t>mol%</t>
-  </si>
-  <si>
-    <t>C(=O)OO-396000-27.0-56.0-C(=O)OO-C1OC1-7mol%</t>
-  </si>
-  <si>
-    <t>文献 Fig.3b ¹H NMR谱图</t>
-  </si>
-  <si>
-    <t>文献 Fig.5 TEM图</t>
-  </si>
-  <si>
-    <t>文献 Fig.4 Payne效应曲线、文献 Fig.9 拉伸应力-应变曲线</t>
-  </si>
-  <si>
-    <t>文献 Fig.3c DSC曲线</t>
-  </si>
-  <si>
-    <t>Liu C, Guo M, Zhai X, et al. Using Epoxidized Solution Polymerized Styrene-Butadiene Rubbers (ESSBRs) as Coupling Agents to Modify Silica without Volatile Organic Compounds[J]. Polymers, 2020, 12(6): 1257.</t>
-  </si>
-  <si>
-    <t>10.3390/polym12061257</t>
-  </si>
-  <si>
-    <t>SSBR-064</t>
-  </si>
-  <si>
-    <t>绿色轮胎、抗湿滑与抗老化</t>
-  </si>
-  <si>
-    <t>对苯二胺 (PPD) 改性氧化石墨烯</t>
-  </si>
-  <si>
-    <t>C1=CC(=CC=C1N)N.[*]c1ccccc1O[*]</t>
-  </si>
-  <si>
-    <t>C1=CC(=CC=C1N)N.[*]c1ccccc1O[*]---------N--</t>
-  </si>
-  <si>
-    <t>Wan S, Lu X, Zhao H, et al. Effect of Graphene Oxide Modified with Organic Amine on the Aging Resistance, Rolling Loss and Wet-skid Resistance of Solution Polymerized Styrene-Butadiene Rubber[J]. Materials, 2020, 13(5): 1025.</t>
-  </si>
-  <si>
-    <t>10.3390/ma13051025</t>
-  </si>
-  <si>
-    <t>SSBR-065</t>
-  </si>
-  <si>
-    <t>形状记忆、自修复高强韧弹性体</t>
-  </si>
-  <si>
-    <t>三唑啉二酮 (TAD)</t>
-  </si>
-  <si>
-    <t>O=C1N=NC(=O)N1</t>
-  </si>
-  <si>
-    <t>碳碳双键</t>
-  </si>
-  <si>
-    <t>C=C</t>
-  </si>
-  <si>
-    <t>NC(=O)N</t>
-  </si>
-  <si>
-    <t>脲唑基</t>
-  </si>
-  <si>
-    <t>-NHCONH-</t>
-  </si>
-  <si>
-    <t>O=C1N=NC(=O)N1-------C=C-NC(=O)N--</t>
-  </si>
-  <si>
-    <t>Huang J, Zhang L, Tang Z, et al. Bioinspired Design of a Robust Elastomer with Adaptive Recovery via Triazolinedione Click Chemistry[J]. Macromolecular Rapid Communications, 2017.</t>
-  </si>
-  <si>
-    <t>10.1002/marc.201600678</t>
-  </si>
-  <si>
-    <t>SSBR-068</t>
-  </si>
-  <si>
-    <t>膨胀石墨/橡胶纳米复合材料</t>
-  </si>
-  <si>
-    <t>羧基化丁苯橡胶 (XSBR) 作为增容剂</t>
-  </si>
-  <si>
-    <t>C1=CC=CC=C1.C1=CC(CCC1C=C)C(=O)O</t>
-  </si>
-  <si>
-    <t>C1=CC=CC=C1.C1=CC(CCC1C=C)C(=O)O---------C(=O)O--</t>
-  </si>
-  <si>
-    <t>Malas A, Das C K. Development of Modified Expanded Graphite-Filled Solution Polymerized Styrene Butadiene Rubber Vulcanizates in the Presence and Absence of Carbon Black[J]. Polymer Engineering &amp; Science, 2014, 54: 33-41.</t>
-  </si>
-  <si>
-    <t>10.1002/pen.23533</t>
-  </si>
-  <si>
-    <t>SSBR-069</t>
-  </si>
-  <si>
-    <t>纳米白炭黑分散改性</t>
-  </si>
-  <si>
-    <t>二苯胍 (DPG)</t>
-  </si>
-  <si>
-    <t>c1ccc(NC(=Nc2ccccc2)N)cc1</t>
-  </si>
-  <si>
-    <t>NC(=Nc1ccccc1)Nc2ccccc2</t>
-  </si>
-  <si>
-    <t>胍基</t>
-  </si>
-  <si>
-    <t>-C(=NPh)(NHPh)</t>
-  </si>
-  <si>
-    <t>c1ccc(NC(=Nc2ccccc2)N)cc1---------NC(=Nc1ccccc1)Nc2ccccc2--</t>
-  </si>
-  <si>
-    <t>Mao Y, Tian Q, Zhang C, et al. Vulcanization Accelerator Functionalized Nanosilica: Effect on the Reinforcement Behavior of SSBR/BR[J]. Polymer Engineering &amp; Science, 2019.</t>
-  </si>
-  <si>
-    <t>10.1002/pen.25110</t>
-  </si>
-  <si>
-    <t>SSBR-071</t>
-  </si>
-  <si>
-    <t>白炭黑/SSBR 混炼界面偶联</t>
-  </si>
-  <si>
-    <t>Si747 (硅烷偶联剂)</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSSSCCCO[Si](OCC)(OCC)OCC)(OCC)OCC</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSSSCCCO[Si](OCC)(OCC)OCC)(OCC)OCC---------[Si](OCC)(OCC)OCC--</t>
-  </si>
-  <si>
-    <t>Tao Y C, Dong B, Zhang L Q, et al. REACTIONS OF SILICA-SILANE RUBBER AND PROPERTIES OF SILANE-SILICA/SOLUTION-POLYMERIZED STYRENE-BUTADIENE RUBBER COMPOSITE[J]. Rubber Chemistry and Technology, 2016, 89(3): 526-539.</t>
-  </si>
-  <si>
-    <t>10.5254/rct.16.84812</t>
-  </si>
-  <si>
-    <t>SSBR-075</t>
-  </si>
-  <si>
-    <t>轮胎胎面胶硅烷化研究</t>
-  </si>
-  <si>
-    <t>TESPT</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSSSCCCC[Si](OCC)(OCC)OCC)(OCC)OCC</t>
-  </si>
-  <si>
-    <t>硅烷基</t>
-  </si>
-  <si>
-    <t>CCO[Si](CCCSSSSCCCC[Si](OCC)(OCC)OCC)(OCC)OCC---------[Si](OCC)(OCC)OCC--</t>
-  </si>
-  <si>
-    <t>Jin J, Noordermeer J W M, Dierkes W K, et al. The Effect of Silanization Temperature and Time on the Marching Modulus of Silica-Filled Tire Tread Compounds[J]. Polymers, 2020, 12(1): 209.</t>
-  </si>
-  <si>
-    <t>10.3390/polym12010209</t>
-  </si>
-  <si>
-    <t>SSBR-076</t>
-  </si>
-  <si>
-    <t>绿色轮胎、白炭黑改性</t>
-  </si>
-  <si>
-    <t>间氯过氧苯甲酸 (m-CPBA)</t>
-  </si>
-  <si>
-    <t>Clc1cccc(C(=O)OO)c1</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Clc1cccc(C(=O)OO)c1-100000-21.0-63.0---C1OC1-7%</t>
-  </si>
-  <si>
-    <t>文献 Fig.11</t>
-  </si>
-  <si>
-    <t>SSBR-078</t>
-  </si>
-  <si>
-    <t>生物基橡胶、高性能轮胎</t>
-  </si>
-  <si>
-    <t>CC(=C)C=CC=C(C)C</t>
-  </si>
-  <si>
-    <t>萜烯基</t>
-  </si>
-  <si>
-    <t>-萜烯-</t>
-  </si>
-  <si>
-    <t>CC(C)=CCCC(=C)C=C-246000-------CC(=C)C=CC=C(C)C--</t>
-  </si>
-  <si>
-    <t>文献 Fig.6 TEM图</t>
-  </si>
-  <si>
-    <t>Zhang J, Lu J, Wang D, et al. Preparation, carbon black dispersibility and performances of novel biobased integral solution-polymerized styrene-butadiene rubber with β-myrcene bottlebrush segments[J]. Journal of Materials Science, 2020, 55.</t>
-  </si>
-  <si>
-    <t>10.1007/s10853-020-05218-w</t>
-  </si>
-  <si>
-    <t>SSBR-079</t>
-  </si>
-  <si>
-    <t>EVA 改性白炭黑</t>
-  </si>
-  <si>
-    <t>C1=CC(=O)OC1.CC(=O)O.[O-][Si]([O-])([O-])[O-]</t>
-  </si>
-  <si>
-    <t>CC(=O)OC=C</t>
-  </si>
-  <si>
-    <t>酯基/乙烯基</t>
-  </si>
-  <si>
-    <t>-OCOCH₃/-CH=CH₂</t>
-  </si>
-  <si>
-    <t>C1=CC(=O)OC1.CC(=O)O.[O-][Si]([O-])([O-])[O-]---------CC(=O)OC=C--</t>
   </si>
   <si>
     <t>Tang Y, Tian Q F, Liu Y L, et al. Application of carboxylated ethylene/vinyl acetate copolymer-modified nanosilica in tire tread rubber[J]. Iranian Polymer Journal, 2020.</t>
@@ -2068,7 +2047,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2135,20 +2114,20 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -2464,7 +2443,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -3003,15 +2982,13 @@
         <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="D8" s="6">
-        <v>20.1</v>
+        <v>23.5</v>
       </c>
       <c r="E8" s="7"/>
-      <c r="F8" s="5">
-        <v>196000</v>
-      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="4" t="s">
         <v>81</v>
       </c>
@@ -3019,111 +2996,99 @@
         <v>82</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="L8" s="4" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O8" s="6">
-        <v>5.1</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="O8" s="6"/>
+      <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="R8" s="4"/>
       <c r="S8" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="U8" s="4"/>
       <c r="V8" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="X8" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.25">
       <c r="A9" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="6">
-        <v>23.5</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D9" s="6"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>30</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>96</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
       <c r="U9" s="4"/>
       <c r="V9" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="X9" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
       <c r="A10" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>25</v>
@@ -3131,51 +3096,51 @@
       <c r="C10" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
       <c r="V10" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="X10" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25">
       <c r="A11" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>25</v>
@@ -3184,64 +3149,58 @@
         <v>66</v>
       </c>
       <c r="D11" s="6">
-        <v>20.1</v>
+        <v>24</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="5">
-        <v>196000</v>
+        <v>168000</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="O11" s="6">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="P11" s="4" t="s">
         <v>34</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
       <c r="V11" s="4" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="X11" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
       <c r="A12" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>25</v>
@@ -3250,18 +3209,22 @@
         <v>25</v>
       </c>
       <c r="D12" s="6">
-        <v>23.5</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+        <v>23.4</v>
+      </c>
+      <c r="E12" s="7">
+        <v>47.3</v>
+      </c>
+      <c r="F12" s="7">
+        <v>223900</v>
+      </c>
       <c r="G12" s="4" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>29</v>
@@ -3270,220 +3233,218 @@
         <v>30</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="O12" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="Q12" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="R12" s="4"/>
+        <v>120</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="S12" s="4" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="X12" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.25">
       <c r="A13" s="4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="D13" s="7">
+        <v>27</v>
+      </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O13" s="8">
+        <v>14.8</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="R13" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="S13" s="4"/>
+      <c r="S13" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
       <c r="V13" s="4" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="X13" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.25">
       <c r="A14" s="4" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="D14" s="5">
-        <v>24</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="5">
-        <v>168000</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E14" s="7">
+        <v>26</v>
+      </c>
+      <c r="F14" s="5"/>
       <c r="G14" s="4" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O14" s="6"/>
+      <c r="P14" s="4"/>
       <c r="Q14" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>107</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="R14" s="4"/>
       <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
+      <c r="T14" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="U14" s="4"/>
       <c r="V14" s="4" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="X14" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
       <c r="A15" s="4" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="6">
-        <v>23.4</v>
-      </c>
-      <c r="E15" s="6">
-        <v>47.3</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="5">
-        <v>223900</v>
+        <v>150000</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>30</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>47</v>
+        <v>151</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="O15" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O15" s="6"/>
+      <c r="P15" s="4"/>
       <c r="Q15" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>133</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
       <c r="T15" s="4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="4" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="X15" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>25</v>
@@ -3492,18 +3453,20 @@
         <v>25</v>
       </c>
       <c r="D16" s="5">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="F16" s="7">
+        <v>206600</v>
+      </c>
       <c r="G16" s="4" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>29</v>
@@ -3512,42 +3475,46 @@
         <v>30</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="O16" s="6">
-        <v>14.8</v>
+        <v>2.4</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
+        <v>159</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="V16" s="4" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="X16" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>25</v>
@@ -3556,54 +3523,64 @@
         <v>25</v>
       </c>
       <c r="D17" s="5">
-        <v>36</v>
-      </c>
-      <c r="E17" s="5">
-        <v>26</v>
-      </c>
-      <c r="F17" s="7"/>
+        <v>20.7</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7">
+        <v>214700</v>
+      </c>
       <c r="G17" s="4" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+        <v>118</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="L17" s="4" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>152</v>
+        <v>47</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="O17" s="8"/>
-      <c r="P17" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="O17" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="Q17" s="4" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="U17" s="4"/>
+      <c r="S17" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="V17" s="4" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="X17" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="4" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>25</v>
@@ -3611,53 +3588,59 @@
       <c r="C18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="9"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="5">
-        <v>150000</v>
-      </c>
+      <c r="F18" s="5"/>
       <c r="G18" s="4" t="s">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+        <v>173</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="L18" s="4" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
+        <v>179</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="T18" s="4" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="X18" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>25</v>
@@ -3665,21 +3648,19 @@
       <c r="C19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="5">
-        <v>21</v>
-      </c>
+      <c r="D19" s="5"/>
       <c r="E19" s="7"/>
       <c r="F19" s="5">
-        <v>206600</v>
+        <v>160200</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>29</v>
@@ -3688,112 +3669,102 @@
         <v>30</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="O19" s="6">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="P19" s="4" t="s">
         <v>34</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>172</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="U19" s="4"/>
       <c r="V19" s="4" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="X19" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D20" s="6">
-        <v>20.7</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="5">
-        <v>214700</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E20" s="7">
+        <v>50</v>
+      </c>
+      <c r="F20" s="5"/>
       <c r="G20" s="4" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>30</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
       <c r="L20" s="4" t="s">
-        <v>46</v>
+        <v>199</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="O20" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="O20" s="6"/>
+      <c r="P20" s="4"/>
       <c r="Q20" s="4" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4" t="s">
-        <v>96</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="U20" s="4"/>
       <c r="V20" s="4" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="X20" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>25</v>
@@ -3801,125 +3772,121 @@
       <c r="C21" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="7"/>
+      <c r="D21" s="7">
+        <v>25</v>
+      </c>
+      <c r="E21" s="7">
+        <v>50</v>
+      </c>
       <c r="F21" s="7"/>
       <c r="G21" s="4" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>186</v>
+        <v>30</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="O21" s="8"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>191</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
       <c r="T21" s="4" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="4" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="X21" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="5">
-        <v>160200</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D22" s="7">
+        <v>25</v>
+      </c>
+      <c r="E22" s="7">
+        <v>50</v>
+      </c>
+      <c r="F22" s="5"/>
       <c r="G22" s="4" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>112</v>
+        <v>220</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>29</v>
+        <v>221</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>30</v>
+        <v>222</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>92</v>
+        <v>223</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>93</v>
+        <v>224</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O22" s="5">
-        <v>10</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>34</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O22" s="5"/>
+      <c r="P22" s="4"/>
       <c r="Q22" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>199</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="R22" s="4"/>
       <c r="S22" s="4" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="4" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="X22" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>25</v>
@@ -3935,49 +3902,53 @@
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="4" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
+        <v>234</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>236</v>
+      </c>
       <c r="L23" s="4" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="O23" s="8"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="4" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="X23" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>25</v>
@@ -3986,58 +3957,60 @@
         <v>66</v>
       </c>
       <c r="D24" s="5">
-        <v>25</v>
+        <v>21.1</v>
       </c>
       <c r="E24" s="5">
-        <v>50</v>
-      </c>
-      <c r="F24" s="7"/>
+        <v>38.1</v>
+      </c>
+      <c r="F24" s="7">
+        <v>258000</v>
+      </c>
       <c r="G24" s="4" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>30</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
       <c r="L24" s="4" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
+      <c r="S24" s="4" t="s">
+        <v>253</v>
+      </c>
       <c r="T24" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="U24" s="4"/>
+        <v>254</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>255</v>
+      </c>
       <c r="V24" s="4" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="X24" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>25</v>
@@ -4046,60 +4019,60 @@
         <v>66</v>
       </c>
       <c r="D25" s="5">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="E25" s="5">
-        <v>50</v>
-      </c>
-      <c r="F25" s="7"/>
+        <v>46</v>
+      </c>
+      <c r="F25" s="7">
+        <v>336000</v>
+      </c>
       <c r="G25" s="4" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>231</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
       <c r="L25" s="4" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="O25" s="8"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="U25" s="4"/>
+        <v>254</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>255</v>
+      </c>
       <c r="V25" s="4" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="X25" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>25</v>
@@ -4108,60 +4081,60 @@
         <v>66</v>
       </c>
       <c r="D26" s="5">
-        <v>25</v>
+        <v>29.5</v>
       </c>
       <c r="E26" s="5">
-        <v>50</v>
-      </c>
-      <c r="F26" s="7"/>
+        <v>34.7</v>
+      </c>
+      <c r="F26" s="7">
+        <v>351000</v>
+      </c>
       <c r="G26" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
       <c r="L26" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O26" s="8"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="U26" s="4"/>
+        <v>254</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>255</v>
+      </c>
       <c r="V26" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="W26" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="X26" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>25</v>
@@ -4170,60 +4143,52 @@
         <v>66</v>
       </c>
       <c r="D27" s="6">
-        <v>21.1</v>
-      </c>
-      <c r="E27" s="6">
-        <v>38.1</v>
-      </c>
-      <c r="F27" s="5">
-        <v>258000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="5"/>
       <c r="G27" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4" t="s">
-        <v>258</v>
+        <v>55</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>260</v>
+        <v>57</v>
       </c>
       <c r="O27" s="8"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="R27" s="4"/>
-      <c r="S27" s="4" t="s">
-        <v>262</v>
-      </c>
+      <c r="S27" s="4"/>
       <c r="T27" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="U27" s="4" t="s">
-        <v>264</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="U27" s="4"/>
       <c r="V27" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="W27" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="X27" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>25</v>
@@ -4232,60 +4197,60 @@
         <v>66</v>
       </c>
       <c r="D28" s="6">
-        <v>24.2</v>
+        <v>27.5</v>
       </c>
       <c r="E28" s="5">
-        <v>46</v>
+        <v>25.4</v>
       </c>
       <c r="F28" s="5">
-        <v>336000</v>
+        <v>123000</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="O28" s="8"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="4" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="V28" s="4" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="W28" s="4" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="X28" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>25</v>
@@ -4294,60 +4259,62 @@
         <v>66</v>
       </c>
       <c r="D29" s="6">
-        <v>29.5</v>
+        <v>24.8</v>
       </c>
       <c r="E29" s="6">
-        <v>34.7</v>
+        <v>9.7</v>
       </c>
       <c r="F29" s="5">
-        <v>351000</v>
+        <v>167000</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="O29" s="8"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="R29" s="4"/>
+        <v>289</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>290</v>
+      </c>
       <c r="S29" s="4" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="V29" s="4" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="W29" s="4" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="X29" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>25</v>
@@ -4356,52 +4323,60 @@
         <v>66</v>
       </c>
       <c r="D30" s="5">
-        <v>25</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+        <v>29.5</v>
+      </c>
+      <c r="E30" s="7">
+        <v>34.7</v>
+      </c>
+      <c r="F30" s="7">
+        <v>351000</v>
+      </c>
       <c r="G30" s="4" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4" t="s">
-        <v>55</v>
+        <v>249</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>56</v>
+        <v>250</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>57</v>
+        <v>251</v>
       </c>
       <c r="O30" s="8"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
+        <v>261</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="S30" s="4" t="s">
+        <v>299</v>
+      </c>
       <c r="T30" s="4" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="U30" s="4"/>
       <c r="V30" s="4" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="W30" s="4" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="X30" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>25</v>
@@ -4410,60 +4385,58 @@
         <v>66</v>
       </c>
       <c r="D31" s="6">
-        <v>27.5</v>
+        <v>34.6</v>
       </c>
       <c r="E31" s="6">
-        <v>25.4</v>
-      </c>
-      <c r="F31" s="5">
-        <v>123000</v>
-      </c>
+        <v>40.1</v>
+      </c>
+      <c r="F31" s="5"/>
       <c r="G31" s="4" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="O31" s="8"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="R31" s="4"/>
       <c r="S31" s="4" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="V31" s="4" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="W31" s="4" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="X31" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>25</v>
@@ -4471,63 +4444,55 @@
       <c r="C32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="6">
-        <v>24.8</v>
-      </c>
-      <c r="E32" s="6">
-        <v>9.7</v>
-      </c>
-      <c r="F32" s="5">
-        <v>167000</v>
-      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="5"/>
       <c r="G32" s="4" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>296</v>
+        <v>32</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>297</v>
+        <v>33</v>
       </c>
       <c r="O32" s="8"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="R32" s="4" t="s">
-        <v>299</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="R32" s="4"/>
       <c r="S32" s="4" t="s">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="V32" s="4" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="W32" s="4" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="X32" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>25</v>
@@ -4535,61 +4500,55 @@
       <c r="C33" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="6">
-        <v>29.5</v>
-      </c>
-      <c r="E33" s="6">
-        <v>34.7</v>
-      </c>
-      <c r="F33" s="5">
-        <v>351000</v>
-      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="5"/>
       <c r="G33" s="4" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="O33" s="8"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="S33" s="4" t="s">
-        <v>308</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="S33" s="4"/>
       <c r="T33" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="U33" s="4"/>
+        <v>333</v>
+      </c>
+      <c r="U33" s="4" t="s">
+        <v>334</v>
+      </c>
       <c r="V33" s="4" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="W33" s="4" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="X33" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>25</v>
@@ -4598,81 +4557,89 @@
         <v>66</v>
       </c>
       <c r="D34" s="6">
-        <v>34.6</v>
+        <v>19.4</v>
       </c>
       <c r="E34" s="6">
-        <v>40.1</v>
-      </c>
-      <c r="F34" s="7"/>
+        <v>48.5</v>
+      </c>
+      <c r="F34" s="7">
+        <v>140000</v>
+      </c>
       <c r="G34" s="4" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4" t="s">
-        <v>295</v>
+        <v>341</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="O34" s="8"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="R34" s="4"/>
-      <c r="S34" s="4" t="s">
-        <v>318</v>
-      </c>
+      <c r="S34" s="4"/>
       <c r="T34" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="U34" s="4" t="s">
-        <v>320</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="U34" s="4"/>
       <c r="V34" s="4" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="W34" s="4" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="X34" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="D35" s="7">
+        <v>20.2</v>
+      </c>
+      <c r="E35" s="7">
+        <v>44.6</v>
+      </c>
+      <c r="F35" s="7">
+        <v>395000</v>
+      </c>
       <c r="G35" s="4" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="L35" s="4" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>32</v>
@@ -4680,32 +4647,38 @@
       <c r="N35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O35" s="8"/>
-      <c r="P35" s="4"/>
+      <c r="O35" s="8">
+        <v>7.8</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="Q35" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4" t="s">
-        <v>75</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="R35" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="S35" s="4"/>
       <c r="T35" s="4" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="U35" s="4" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="V35" s="4" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="W35" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="X35" s="4"/>
+        <v>356</v>
+      </c>
+      <c r="X35" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>25</v>
@@ -4713,317 +4686,285 @@
       <c r="C36" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D36" s="9"/>
+      <c r="D36" s="7">
+        <v>25</v>
+      </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="4" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
+        <v>360</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>341</v>
+      </c>
       <c r="L36" s="4" t="s">
-        <v>337</v>
+        <v>96</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>338</v>
+        <v>97</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="O36" s="8"/>
       <c r="P36" s="4"/>
       <c r="Q36" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="R36" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="S36" s="4"/>
+        <v>362</v>
+      </c>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4" t="s">
+        <v>363</v>
+      </c>
       <c r="T36" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="U36" s="4" t="s">
-        <v>343</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="U36" s="4"/>
       <c r="V36" s="4" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="W36" s="4" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="X36" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="D37" s="6">
-        <v>19.4</v>
+        <v>27</v>
       </c>
       <c r="E37" s="6">
-        <v>48.5</v>
+        <v>56</v>
       </c>
       <c r="F37" s="5">
-        <v>140000</v>
+        <v>396000</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>347</v>
+        <v>26</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
+        <v>369</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>369</v>
+      </c>
       <c r="L37" s="4" t="s">
-        <v>350</v>
+        <v>199</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>351</v>
+        <v>200</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="O37" s="8"/>
-      <c r="P37" s="4"/>
+        <v>201</v>
+      </c>
+      <c r="O37" s="8">
+        <v>7</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>371</v>
+      </c>
       <c r="Q37" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
+        <v>372</v>
+      </c>
+      <c r="R37" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="S37" s="4" t="s">
+        <v>374</v>
+      </c>
       <c r="T37" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="U37" s="4"/>
+        <v>375</v>
+      </c>
+      <c r="U37" s="4" t="s">
+        <v>376</v>
+      </c>
       <c r="V37" s="4" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="W37" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="X37" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D38" s="6">
-        <v>20.2</v>
-      </c>
-      <c r="E38" s="6">
-        <v>44.6</v>
-      </c>
-      <c r="F38" s="5">
-        <v>395000</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="5"/>
       <c r="G38" s="4" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>30</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
       <c r="L38" s="4" t="s">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38" s="6">
-        <v>7.8</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>131</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O38" s="6"/>
+      <c r="P38" s="4"/>
       <c r="Q38" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="R38" s="4" t="s">
-        <v>361</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="R38" s="4"/>
       <c r="S38" s="4"/>
-      <c r="T38" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="U38" s="4" t="s">
-        <v>84</v>
-      </c>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
       <c r="V38" s="4" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="W38" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="X38" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="X38" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="5">
-        <v>25</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D39" s="5"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="4" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>103</v>
+        <v>392</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>104</v>
+        <v>393</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="O39" s="8"/>
       <c r="P39" s="4"/>
       <c r="Q39" s="4" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="R39" s="4"/>
-      <c r="S39" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="T39" s="4" t="s">
-        <v>372</v>
-      </c>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
       <c r="U39" s="4"/>
       <c r="V39" s="4" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="W39" s="4" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="X39" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="5">
-        <v>27</v>
-      </c>
-      <c r="E40" s="5">
-        <v>56</v>
-      </c>
-      <c r="F40" s="5">
-        <v>396000</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
       <c r="G40" s="4" t="s">
-        <v>26</v>
+        <v>399</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>377</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
       <c r="L40" s="4" t="s">
-        <v>208</v>
+        <v>46</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>209</v>
+        <v>47</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="O40" s="5">
-        <v>7</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>379</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="O40" s="5"/>
+      <c r="P40" s="4"/>
       <c r="Q40" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="R40" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="S40" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="T40" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="U40" s="4" t="s">
-        <v>384</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
       <c r="V40" s="4" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="W40" s="4" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="X40" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>25</v>
@@ -5031,103 +4972,99 @@
       <c r="C41" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="9"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="4" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4" t="s">
-        <v>103</v>
+        <v>409</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>104</v>
+        <v>410</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="O41" s="8"/>
       <c r="P41" s="4"/>
       <c r="Q41" s="4" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="W41" s="4" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="X41" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" s="9"/>
+        <v>66</v>
+      </c>
+      <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="4" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>399</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
       <c r="L42" s="4" t="s">
-        <v>400</v>
+        <v>55</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>401</v>
+        <v>56</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>402</v>
+        <v>57</v>
       </c>
       <c r="O42" s="8"/>
       <c r="P42" s="4"/>
       <c r="Q42" s="4" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="R42" s="4"/>
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
       <c r="V42" s="4" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="W42" s="4" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="X42" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>25</v>
@@ -5135,99 +5072,117 @@
       <c r="C43" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D43" s="9"/>
+      <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="4" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>47</v>
+        <v>426</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>48</v>
+        <v>343</v>
       </c>
       <c r="O43" s="8"/>
       <c r="P43" s="4"/>
       <c r="Q43" s="4" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="R43" s="4"/>
       <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
+      <c r="T43" s="4" t="s">
+        <v>354</v>
+      </c>
       <c r="U43" s="4"/>
       <c r="V43" s="4" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="W43" s="4" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="X43" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="D44" s="7">
+        <v>21</v>
+      </c>
+      <c r="E44" s="7">
+        <v>63</v>
+      </c>
+      <c r="F44" s="7">
+        <v>100000</v>
+      </c>
       <c r="G44" s="4" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4" t="s">
-        <v>417</v>
+        <v>199</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>418</v>
+        <v>200</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="O44" s="8"/>
-      <c r="P44" s="4"/>
+        <v>201</v>
+      </c>
+      <c r="O44" s="8">
+        <v>7</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="Q44" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
+        <v>435</v>
+      </c>
+      <c r="R44" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="S44" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="T44" s="4" t="s">
+        <v>436</v>
+      </c>
       <c r="U44" s="4"/>
       <c r="V44" s="4" t="s">
-        <v>421</v>
+        <v>377</v>
       </c>
       <c r="W44" s="4" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="X44" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>25</v>
@@ -5235,49 +5190,55 @@
       <c r="C45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D45" s="9"/>
+      <c r="D45" s="7"/>
       <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
+      <c r="F45" s="7">
+        <v>246000</v>
+      </c>
       <c r="G45" s="4" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>425</v>
+        <v>148</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>426</v>
+        <v>149</v>
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4" t="s">
-        <v>55</v>
+        <v>439</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>56</v>
+        <v>440</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>57</v>
+        <v>441</v>
       </c>
       <c r="O45" s="8"/>
       <c r="P45" s="4"/>
       <c r="Q45" s="4" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
+      <c r="S45" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="T45" s="4" t="s">
+        <v>354</v>
+      </c>
       <c r="U45" s="4"/>
       <c r="V45" s="4" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="W45" s="4" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="X45" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>25</v>
@@ -5285,173 +5246,175 @@
       <c r="C46" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D46" s="9"/>
+      <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="4" t="s">
-        <v>431</v>
+        <v>136</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4" t="s">
-        <v>55</v>
+        <v>449</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
       <c r="O46" s="8"/>
       <c r="P46" s="4"/>
       <c r="Q46" s="4" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4" t="s">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="U46" s="4"/>
       <c r="V46" s="4" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="W46" s="4" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="X46" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47" s="5">
-        <v>21</v>
-      </c>
-      <c r="E47" s="5">
-        <v>63</v>
-      </c>
-      <c r="F47" s="5">
-        <v>100000</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="4" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4" t="s">
-        <v>208</v>
+        <v>460</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>209</v>
+        <v>85</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="O47" s="5">
-        <v>7</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>442</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="O47" s="5"/>
+      <c r="P47" s="4"/>
       <c r="Q47" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="R47" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="S47" s="4" t="s">
-        <v>96</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
       <c r="T47" s="4" t="s">
-        <v>444</v>
+        <v>354</v>
       </c>
       <c r="U47" s="4"/>
       <c r="V47" s="4" t="s">
-        <v>385</v>
+        <v>463</v>
       </c>
       <c r="W47" s="4" t="s">
-        <v>386</v>
+        <v>464</v>
       </c>
       <c r="X47" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="D48" s="7">
+        <v>10</v>
+      </c>
+      <c r="E48" s="7">
+        <v>41</v>
+      </c>
       <c r="F48" s="5">
-        <v>246000</v>
+        <v>161000</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>159</v>
+        <v>467</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
+        <v>468</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>391</v>
+      </c>
       <c r="L48" s="4" t="s">
-        <v>447</v>
+        <v>469</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="O48" s="8"/>
-      <c r="P48" s="4"/>
+        <v>471</v>
+      </c>
+      <c r="O48" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="Q48" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4" t="s">
-        <v>451</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="R48" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="S48" s="4"/>
       <c r="T48" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="U48" s="4"/>
+        <v>345</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="V48" s="4" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="W48" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="X48" s="4"/>
+        <v>475</v>
+      </c>
+      <c r="X48" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>25</v>
@@ -5459,51 +5422,49 @@
       <c r="C49" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D49" s="9"/>
+      <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
       <c r="G49" s="4" t="s">
-        <v>148</v>
+        <v>477</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="O49" s="8"/>
       <c r="P49" s="4"/>
       <c r="Q49" s="4" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="4"/>
-      <c r="T49" s="4" t="s">
-        <v>85</v>
-      </c>
+      <c r="T49" s="4"/>
       <c r="U49" s="4"/>
       <c r="V49" s="4" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="W49" s="4" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="X49" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>25</v>
@@ -5511,51 +5472,55 @@
       <c r="C50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="7"/>
+      <c r="D50" s="7">
+        <v>24.6</v>
+      </c>
+      <c r="E50" s="7">
+        <v>47.9</v>
+      </c>
       <c r="F50" s="7"/>
       <c r="G50" s="4" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4" t="s">
-        <v>467</v>
+        <v>96</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="O50" s="8"/>
       <c r="P50" s="4"/>
       <c r="Q50" s="4" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="R50" s="4"/>
       <c r="S50" s="4"/>
       <c r="T50" s="4" t="s">
-        <v>84</v>
+        <v>491</v>
       </c>
       <c r="U50" s="4"/>
       <c r="V50" s="4" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="W50" s="4" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="X50" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>25</v>
@@ -5564,120 +5529,128 @@
         <v>25</v>
       </c>
       <c r="D51" s="5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E51" s="5">
-        <v>41</v>
-      </c>
-      <c r="F51" s="5">
-        <v>161000</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F51" s="5"/>
       <c r="G51" s="4" t="s">
-        <v>473</v>
+        <v>26</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>476</v>
+        <v>199</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>477</v>
+        <v>200</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="O51" s="8" t="s">
-        <v>479</v>
+        <v>201</v>
+      </c>
+      <c r="O51" s="9">
+        <v>8</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="R51" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="S51" s="4"/>
+        <v>180</v>
+      </c>
+      <c r="S51" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="T51" s="4" t="s">
-        <v>354</v>
+        <v>436</v>
       </c>
       <c r="U51" s="4" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="W51" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="X51" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="X51" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="D52" s="7"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="4" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
+        <v>503</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="L52" s="4" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="O52" s="8"/>
       <c r="P52" s="4"/>
       <c r="Q52" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="R52" s="4"/>
+        <v>508</v>
+      </c>
+      <c r="R52" s="4" t="s">
+        <v>354</v>
+      </c>
       <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
+      <c r="T52" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>453</v>
+      </c>
       <c r="V52" s="4" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="W52" s="4" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="X52" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>25</v>
@@ -5685,125 +5658,107 @@
       <c r="C53" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D53" s="6">
-        <v>24.6</v>
-      </c>
-      <c r="E53" s="6">
-        <v>47.9</v>
-      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
       <c r="F53" s="7"/>
       <c r="G53" s="4" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4" t="s">
-        <v>103</v>
+        <v>515</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>104</v>
+        <v>516</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>369</v>
+        <v>517</v>
       </c>
       <c r="O53" s="8"/>
       <c r="P53" s="4"/>
       <c r="Q53" s="4" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
+      <c r="S53" s="4" t="s">
+        <v>374</v>
+      </c>
       <c r="T53" s="4" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="U53" s="4"/>
       <c r="V53" s="4" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="W53" s="4" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="X53" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D54" s="5">
-        <v>25</v>
-      </c>
-      <c r="E54" s="5">
-        <v>57</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
       <c r="F54" s="7"/>
       <c r="G54" s="4" t="s">
-        <v>26</v>
+        <v>523</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>399</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
       <c r="L54" s="4" t="s">
-        <v>208</v>
+        <v>30</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>209</v>
+        <v>526</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="O54" s="5">
-        <v>8</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>442</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="O54" s="5"/>
+      <c r="P54" s="4"/>
       <c r="Q54" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="R54" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="R54" s="4"/>
       <c r="S54" s="4" t="s">
-        <v>75</v>
+        <v>529</v>
       </c>
       <c r="T54" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="U54" s="4" t="s">
-        <v>134</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="U54" s="4"/>
       <c r="V54" s="4" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="W54" s="4" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="X54" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>25</v>
@@ -5811,59 +5766,69 @@
       <c r="C55" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
+      <c r="D55" s="7">
+        <v>21</v>
+      </c>
+      <c r="E55" s="7">
+        <v>63</v>
+      </c>
+      <c r="F55" s="7">
+        <v>100000</v>
+      </c>
       <c r="G55" s="4" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>31</v>
+        <v>538</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="O55" s="8"/>
-      <c r="P55" s="4"/>
+        <v>541</v>
+      </c>
+      <c r="O55" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="Q55" s="4" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="R55" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="S55" s="4"/>
+        <v>453</v>
+      </c>
+      <c r="S55" s="4" t="s">
+        <v>544</v>
+      </c>
       <c r="T55" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="U55" s="4" t="s">
-        <v>85</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="U55" s="4"/>
       <c r="V55" s="4" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="W55" s="4" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
       <c r="X55" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>25</v>
@@ -5871,399 +5836,395 @@
       <c r="C56" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="9"/>
+      <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="4" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4" t="s">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="O56" s="8"/>
       <c r="P56" s="4"/>
       <c r="Q56" s="4" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="R56" s="4"/>
-      <c r="S56" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="T56" s="4" t="s">
-        <v>526</v>
-      </c>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
       <c r="U56" s="4"/>
       <c r="V56" s="4" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="W56" s="4" t="s">
-        <v>528</v>
+        <v>557</v>
       </c>
       <c r="X56" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D57" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="D57" s="7">
+        <v>25</v>
+      </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="4" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>531</v>
+        <v>560</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
+        <v>561</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>391</v>
+      </c>
       <c r="L57" s="4" t="s">
-        <v>30</v>
+        <v>199</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>533</v>
+        <v>200</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="O57" s="8"/>
-      <c r="P57" s="4"/>
+        <v>201</v>
+      </c>
+      <c r="O57" s="8">
+        <v>10.09</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="Q57" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4" t="s">
-        <v>536</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S57" s="4"/>
       <c r="T57" s="4" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
       <c r="U57" s="4"/>
       <c r="V57" s="4" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="W57" s="4" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="X57" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D58" s="5">
-        <v>21</v>
-      </c>
-      <c r="E58" s="5">
-        <v>63</v>
-      </c>
-      <c r="F58" s="5">
-        <v>100000</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
       <c r="G58" s="4" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>545</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
       <c r="L58" s="4" t="s">
-        <v>546</v>
+        <v>199</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>547</v>
+        <v>200</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="O58" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="P58" s="4" t="s">
-        <v>442</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="O58" s="9"/>
+      <c r="P58" s="4"/>
       <c r="Q58" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="R58" s="4" t="s">
-        <v>85</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="R58" s="4"/>
       <c r="S58" s="4" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="T58" s="4" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="U58" s="4"/>
       <c r="V58" s="4" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="W58" s="4" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="X58" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D59" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
       <c r="G59" s="4" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
       <c r="L59" s="4" t="s">
-        <v>559</v>
+        <v>199</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>560</v>
+        <v>200</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>561</v>
+        <v>201</v>
       </c>
       <c r="O59" s="8"/>
       <c r="P59" s="4"/>
       <c r="Q59" s="4" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4"/>
+      <c r="S59" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="T59" s="4" t="s">
+        <v>582</v>
+      </c>
       <c r="U59" s="4"/>
       <c r="V59" s="4" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="W59" s="4" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="X59" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D60" s="5">
-        <v>25</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D60" s="5"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="4" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>567</v>
+        <v>316</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>399</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
       <c r="L60" s="4" t="s">
-        <v>208</v>
+        <v>318</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>209</v>
+        <v>32</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="O60" s="6">
-        <v>10.09</v>
-      </c>
-      <c r="P60" s="4" t="s">
-        <v>442</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="O60" s="6"/>
+      <c r="P60" s="4"/>
       <c r="Q60" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="R60" s="4" t="s">
-        <v>107</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="R60" s="4"/>
       <c r="S60" s="4"/>
       <c r="T60" s="4" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="U60" s="4"/>
       <c r="V60" s="4" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="W60" s="4" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="X60" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="9"/>
-      <c r="E61" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="D61" s="7">
+        <v>25</v>
+      </c>
+      <c r="E61" s="7">
+        <v>57</v>
+      </c>
       <c r="F61" s="7"/>
       <c r="G61" s="4" t="s">
-        <v>574</v>
+        <v>26</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
+        <v>561</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>391</v>
+      </c>
       <c r="L61" s="4" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="O61" s="8"/>
-      <c r="P61" s="4"/>
+        <v>201</v>
+      </c>
+      <c r="O61" s="8">
+        <v>12</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="Q61" s="4" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="R61" s="4"/>
       <c r="S61" s="4" t="s">
-        <v>579</v>
+        <v>374</v>
       </c>
       <c r="T61" s="4" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="U61" s="4"/>
       <c r="V61" s="4" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="W61" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="X61" s="4"/>
+        <v>595</v>
+      </c>
+      <c r="X61" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62" s="9"/>
+        <v>66</v>
+      </c>
+      <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="4" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4" t="s">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>209</v>
+        <v>600</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>210</v>
+        <v>601</v>
       </c>
       <c r="O62" s="8"/>
       <c r="P62" s="4"/>
       <c r="Q62" s="4" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="R62" s="4"/>
       <c r="S62" s="4" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="T62" s="4" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="U62" s="4"/>
       <c r="V62" s="4" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="W62" s="4" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="X62" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>25</v>
@@ -6271,51 +6232,55 @@
       <c r="C63" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D63" s="9"/>
+      <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
       <c r="G63" s="4" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>325</v>
+        <v>609</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>326</v>
+        <v>610</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4" t="s">
-        <v>327</v>
+        <v>611</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>32</v>
+        <v>612</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>33</v>
+        <v>613</v>
       </c>
       <c r="O63" s="8"/>
       <c r="P63" s="4"/>
       <c r="Q63" s="4" t="s">
-        <v>328</v>
+        <v>614</v>
       </c>
       <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
+      <c r="S63" s="4" t="s">
+        <v>615</v>
+      </c>
       <c r="T63" s="4" t="s">
-        <v>594</v>
+        <v>616</v>
       </c>
       <c r="U63" s="4"/>
       <c r="V63" s="4" t="s">
-        <v>595</v>
+        <v>617</v>
       </c>
       <c r="W63" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="X63" s="4"/>
+        <v>618</v>
+      </c>
+      <c r="X63" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>597</v>
+        <v>619</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>25</v>
@@ -6331,113 +6296,121 @@
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="4" t="s">
-        <v>26</v>
+        <v>620</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>568</v>
+        <v>622</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>398</v>
+        <v>623</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>399</v>
+        <v>199</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>208</v>
+        <v>96</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>209</v>
+        <v>97</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>210</v>
+        <v>361</v>
       </c>
       <c r="O64" s="5">
         <v>12</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>442</v>
+        <v>624</v>
       </c>
       <c r="Q64" s="4" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="R64" s="4"/>
       <c r="S64" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="T64" s="4" t="s">
-        <v>600</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="T64" s="4"/>
       <c r="U64" s="4"/>
       <c r="V64" s="4" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="W64" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="X64" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="X64" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D65" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="D65" s="7"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
       <c r="G65" s="4" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
+        <v>631</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>391</v>
+      </c>
       <c r="L65" s="4" t="s">
-        <v>487</v>
+        <v>55</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>607</v>
+        <v>426</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="O65" s="8"/>
-      <c r="P65" s="4"/>
+        <v>343</v>
+      </c>
+      <c r="O65" s="8">
+        <v>10</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="Q65" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="R65" s="4"/>
+        <v>633</v>
+      </c>
+      <c r="R65" s="4" t="s">
+        <v>634</v>
+      </c>
       <c r="S65" s="4" t="s">
-        <v>610</v>
+        <v>75</v>
       </c>
       <c r="T65" s="4" t="s">
-        <v>611</v>
+        <v>635</v>
       </c>
       <c r="U65" s="4"/>
       <c r="V65" s="4" t="s">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="W65" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="X65" s="4"/>
+        <v>637</v>
+      </c>
+      <c r="X65" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>25</v>
@@ -6445,55 +6418,53 @@
       <c r="C66" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D66" s="9"/>
+      <c r="D66" s="7"/>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
       <c r="G66" s="4" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="O66" s="8"/>
       <c r="P66" s="4"/>
       <c r="Q66" s="4" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="R66" s="4"/>
       <c r="S66" s="4" t="s">
-        <v>622</v>
+        <v>75</v>
       </c>
       <c r="T66" s="4" t="s">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="U66" s="4"/>
       <c r="V66" s="4" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="W66" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="X66" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="X66" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="4" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>25</v>
@@ -6502,62 +6473,60 @@
         <v>25</v>
       </c>
       <c r="D67" s="5">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E67" s="5">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="4" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>628</v>
+        <v>651</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>629</v>
+        <v>652</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>208</v>
+        <v>391</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>103</v>
+        <v>341</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>104</v>
+        <v>654</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="O67" s="5">
-        <v>12</v>
-      </c>
-      <c r="P67" s="4" t="s">
-        <v>631</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="O67" s="5"/>
+      <c r="P67" s="4"/>
       <c r="Q67" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="T67" s="4"/>
+        <v>655</v>
+      </c>
+      <c r="R67" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4" t="s">
+        <v>563</v>
+      </c>
       <c r="U67" s="4"/>
       <c r="V67" s="4" t="s">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="W67" s="4" t="s">
-        <v>634</v>
+        <v>657</v>
       </c>
       <c r="X67" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>635</v>
+        <v>658</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>25</v>
@@ -6565,57 +6534,63 @@
       <c r="C68" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D68" s="9"/>
-      <c r="E68" s="7"/>
+      <c r="D68" s="7">
+        <v>25</v>
+      </c>
+      <c r="E68" s="7">
+        <v>57</v>
+      </c>
       <c r="F68" s="7"/>
       <c r="G68" s="4" t="s">
-        <v>636</v>
+        <v>659</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>637</v>
+        <v>591</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>638</v>
+        <v>561</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>639</v>
+        <v>390</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>434</v>
+        <v>200</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>352</v>
+        <v>201</v>
       </c>
       <c r="O68" s="5">
-        <v>10</v>
+        <v>13.8</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="Q68" s="4" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="R68" s="4" t="s">
-        <v>641</v>
+        <v>180</v>
       </c>
       <c r="S68" s="4" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="T68" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="U68" s="4"/>
+        <v>661</v>
+      </c>
+      <c r="U68" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="V68" s="4" t="s">
-        <v>643</v>
+        <v>662</v>
       </c>
       <c r="W68" s="4" t="s">
-        <v>644</v>
+        <v>663</v>
       </c>
       <c r="X68" s="4" t="s">
         <v>42</v>
@@ -6623,253 +6598,65 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>645</v>
+        <v>664</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D69" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="D69" s="7">
+        <v>25</v>
+      </c>
       <c r="E69" s="7"/>
       <c r="F69" s="7"/>
       <c r="G69" s="4" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>647</v>
+        <v>666</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
+        <v>433</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>391</v>
+      </c>
       <c r="L69" s="4" t="s">
-        <v>649</v>
+        <v>199</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>650</v>
+        <v>200</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>651</v>
+        <v>201</v>
       </c>
       <c r="O69" s="8"/>
       <c r="P69" s="4"/>
       <c r="Q69" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="R69" s="4"/>
+        <v>667</v>
+      </c>
+      <c r="R69" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="S69" s="4" t="s">
-        <v>75</v>
+        <v>668</v>
       </c>
       <c r="T69" s="4" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="U69" s="4"/>
       <c r="V69" s="4" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="W69" s="4" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="X69" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D70" s="5">
-        <v>19</v>
-      </c>
-      <c r="E70" s="5">
-        <v>10</v>
-      </c>
-      <c r="F70" s="7"/>
-      <c r="G70" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="M70" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="N70" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="O70" s="8"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="R70" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="U70" s="4"/>
-      <c r="V70" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="W70" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="X70" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D71" s="5">
-        <v>25</v>
-      </c>
-      <c r="E71" s="5">
-        <v>57</v>
-      </c>
-      <c r="F71" s="7"/>
-      <c r="G71" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="L71" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="M71" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="N71" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="O71" s="6">
-        <v>13.8</v>
-      </c>
-      <c r="P71" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q71" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="R71" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="S71" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="T71" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="U71" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="V71" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="W71" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="X71" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D72" s="5">
-        <v>25</v>
-      </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="N72" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="O72" s="8"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="R72" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="S72" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="T72" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="U72" s="4"/>
-      <c r="V72" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="W72" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="X72" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
